--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -163,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -224,6 +224,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -590,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:M100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -682,6 +685,11 @@
           <t>Fonte / URL de Verificação</t>
         </is>
       </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Citação Científica (ABNT-like)</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -744,6 +752,11 @@
           <t>https://www.researchgate.net/publication/280078417_EVIDENCIAS_DE_VIDA_NO_EDIACARANO_INFERIOR_DA_BACIA_DO_ITAJAI_SC ; https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/3142/evidencias_vida.pdf?sequence=1&amp;isAllowed=y (dissertação Zucatti da Rosa) ; https://www.researchgate.net/publication/327289532_PRELIMINARY_REPORT_ON_THE_OCCURRENCE_OF_Chancelloria_sp_IN_THE_ITAJAi_BASIN_SOUTHERN_BRAZIL</t>
         </is>
       </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>ZUCATTI DA ROSA, A.L. 2006. Evidências de vida no Ediacarano inferior da Bacia do Itajaí, SC. Dissertação de Mestrado, Universidade do Vale do Rio dos Sinos (UNISINOS), São Leopoldo, RS, 56 p. [Fonte primária]. Disponível em: https://repositorio.jesuita.org.br/handle/UNISINOS/3142 | DA ROSA, A.L.Z.; NETTO, R.G.; LEIPNITZ, I.I. 1997. Preliminary report on the occurrence of Chancelloria sp. in the Itajaí Basin, southern Brazil. In: Resumos, XI Congresso Brasileiro de Paleontologia, Ribeirão Preto, p. 55. [Fonte primária — publicação em anais de evento]</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -806,6 +819,11 @@
           <t>https://www.researchgate.net/publication/280078417_EVIDENCIAS_DE_VIDA_NO_EDIACARANO_INFERIOR_DA_BACIA_DO_ITAJAI_SC ; https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/3142/evidencias_vida.pdf?sequence=1&amp;isAllowed=y (dissertação Zucatti da Rosa) ; https://www.researchgate.net/publication/327289532_PRELIMINARY_REPORT_ON_THE_OCCURRENCE_OF_Chancelloria_sp_IN_THE_ITAJAi_BASIN_SOUTHERN_BRAZIL</t>
         </is>
       </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>ZUCATTI DA ROSA, A.L. 2006. Evidências de vida no Ediacarano inferior da Bacia do Itajaí, SC. Dissertação de Mestrado, Universidade do Vale do Rio dos Sinos (UNISINOS), São Leopoldo, RS, 56 p. [Fonte primária]. Disponível em: https://repositorio.jesuita.org.br/handle/UNISINOS/3142</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -868,6 +886,11 @@
           <t>https://www.researchgate.net/publication/280078417_EVIDENCIAS_DE_VIDA_NO_EDIACARANO_INFERIOR_DA_BACIA_DO_ITAJAI_SC ; https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/3142/evidencias_vida.pdf?sequence=1&amp;isAllowed=y (dissertação Zucatti da Rosa) ; https://www.researchgate.net/publication/327289532_PRELIMINARY_REPORT_ON_THE_OCCURRENCE_OF_Chancelloria_sp_IN_THE_ITAJAi_BASIN_SOUTHERN_BRAZIL</t>
         </is>
       </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>ZUCATTI DA ROSA, A.L. 2006. Evidências de vida no Ediacarano inferior da Bacia do Itajaí, SC. Dissertação de Mestrado, Universidade do Vale do Rio dos Sinos (UNISINOS), São Leopoldo, RS, 56 p. [Fonte primária]. Disponível em: https://repositorio.jesuita.org.br/handle/UNISINOS/3142</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -930,6 +953,11 @@
           <t>https://www.researchgate.net/publication/280078417_EVIDENCIAS_DE_VIDA_NO_EDIACARANO_INFERIOR_DA_BACIA_DO_ITAJAI_SC ; https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/3142/evidencias_vida.pdf?sequence=1&amp;isAllowed=y (dissertação Zucatti da Rosa) ; https://www.researchgate.net/publication/327289532_PRELIMINARY_REPORT_ON_THE_OCCURRENCE_OF_Chancelloria_sp_IN_THE_ITAJAi_BASIN_SOUTHERN_BRAZIL</t>
         </is>
       </c>
+      <c r="M7" s="21" t="inlineStr">
+        <is>
+          <t>PAIM, P.S.G.; LEIPNITZ, I.I.; DA ROSA, A.L.Z. et al. 1997. Bacia do Itajaí — estratigrafia e registros fossilíferos ediacaranos. In: Resumos, XI Congresso Brasileiro de Paleontologia, Ribeirão Preto, p. 55. [Fonte primária — publicação em anais de evento; publicação em periódico indexado da fonte não localizada no levantamento desta base]</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -992,6 +1020,11 @@
           <t>https://www.researchgate.net/publication/280078417_EVIDENCIAS_DE_VIDA_NO_EDIACARANO_INFERIOR_DA_BACIA_DO_ITAJAI_SC ; https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/3142/evidencias_vida.pdf?sequence=1&amp;isAllowed=y (dissertação Zucatti da Rosa) ; https://www.researchgate.net/publication/327289532_PRELIMINARY_REPORT_ON_THE_OCCURRENCE_OF_Chancelloria_sp_IN_THE_ITAJAi_BASIN_SOUTHERN_BRAZIL</t>
         </is>
       </c>
+      <c r="M8" s="21" t="inlineStr">
+        <is>
+          <t>ZUCATTI DA ROSA, A.L. 2006. Evidências de vida no Ediacarano inferior da Bacia do Itajaí, SC. Dissertação de Mestrado, Universidade do Vale do Rio dos Sinos (UNISINOS), São Leopoldo, RS, 56 p. [Fonte primária]. Disponível em: https://repositorio.jesuita.org.br/handle/UNISINOS/3142</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -1054,6 +1087,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M9" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
@@ -1116,6 +1154,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M10" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -1178,6 +1221,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M11" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
@@ -1240,6 +1288,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M12" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -1302,6 +1355,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M13" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
@@ -1364,6 +1422,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M14" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -1426,6 +1489,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M15" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="40" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
@@ -1488,6 +1556,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M16" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="40" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -1550,6 +1623,11 @@
           <t>https://www.researchgate.net/publication/256186437_Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarare_na_pedreira_de_Aguas_Claras_Santa_Catarina_Brasil ; https://www.academia.edu/3535049/Paleoicnologia_e_a_palinologia_dos_ritmitos_do_Grupo_Itarar%C3%A9_na_pedreira_de_%C3%81guas_Claras_Santa_Catarina_Brasil_</t>
         </is>
       </c>
+      <c r="M17" s="21" t="inlineStr">
+        <is>
+          <t>GANDINI, R.; NETTO, R.G.; SOUZA, P.A. 2007. Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil). Gaea — Journal of Geoscience, 3(2), 47–59. [Fonte primária]. Disponível em: https://www.researchgate.net/publication/256186437</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="40" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
@@ -1612,6 +1690,11 @@
           <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M18" s="21" t="inlineStr">
+        <is>
+          <t>RICHTER, M. 1991. Itacanthus fasciatus n. sp., a palaeonisciform fish from the Lower Permian Lontras Shale of Santa Catarina State, Brazil. Journal of Vertebrate Paleontology, 11(4), 418–430. DOI: 10.1080/02724634.1991.10011414 [Fonte primária]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2 | FIGUEROA, R.T. et al. 2025. [Referência completa não localizada no levantamento desta base — citada em: Researchgate/348390467]</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="40" customHeight="1">
       <c r="A19" s="10" t="inlineStr">
@@ -1674,6 +1757,11 @@
           <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M19" s="21" t="inlineStr">
+        <is>
+          <t>RICHTER, M. 1991. Itacanthus fasciatus n. sp., a palaeonisciform fish from the Lower Permian Lontras Shale of Santa Catarina State, Brazil. Journal of Vertebrate Paleontology, 11(4), 418–430. DOI: 10.1080/02724634.1991.10011414 [Fonte primária]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2 | FIGUEROA, R.T. et al. 2025. [Referência completa não localizada no levantamento desta base — citada em: Researchgate/348390467]</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="40" customHeight="1">
       <c r="A20" s="10" t="inlineStr">
@@ -1736,6 +1824,11 @@
           <t>https://sbpbrasil.org/publications/index.php/rbp/article/view/327 ; https://www.researchgate.net/publication/374930987_A_new_symmoriiform_shark_and_other_chondrichthyan_teeth_from_the_earliest_Permian_of_southern_Brazil</t>
         </is>
       </c>
+      <c r="M20" s="21" t="inlineStr">
+        <is>
+          <t>PAULIV, V.E.; DIAS, E.V.; SEDOR, F.A.; WEINSCHÜTZ, L.C.; RIBEIRO, A.M. 2023. A new symmoriiform shark and other chondrichthyan teeth from the earliest Permian of southern Brazil. Revista Brasileira de Paleontologia, 26(3), 227–237. DOI: 10.4072/rbp.2023.3.07 [Fonte primária]. Disponível em: https://sbpbrasil.org/publications/index.php/rbp/article/view/327</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="40" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -1798,6 +1891,11 @@
           <t>https://sbpbrasil.org/publications/index.php/rbp/article/view/327 ; https://www.researchgate.net/publication/374930987_A_new_symmoriiform_shark_and_other_chondrichthyan_teeth_from_the_earliest_Permian_of_southern_Brazil</t>
         </is>
       </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>PAULIV, V.E.; DIAS, E.V.; SEDOR, F.A.; WEINSCHÜTZ, L.C.; RIBEIRO, A.M. 2023. A new symmoriiform shark and other chondrichthyan teeth from the earliest Permian of southern Brazil. Revista Brasileira de Paleontologia, 26(3), 227–237. DOI: 10.4072/rbp.2023.3.07 [Fonte primária]. Disponível em: https://sbpbrasil.org/publications/index.php/rbp/article/view/327</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
@@ -1860,6 +1958,11 @@
           <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="40" customHeight="1">
       <c r="A23" s="10" t="inlineStr">
@@ -1922,6 +2025,11 @@
           <t>https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
         </is>
       </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>PINTO, I.D.; SEDOR, F.A. 2000. Anthracoblattina mendesi sp. nov. (Blattodea, Phyloblattidae), uma nova barata fóssil do Permocarbonífero brasileiro. Pesquisas em Geociências, 27(1), 41–48. [Fonte primária — verificar volume/paginação em repositório IGeo-UFRGS] | RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
@@ -1984,6 +2092,11 @@
           <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
@@ -2046,6 +2159,11 @@
           <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="40" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
@@ -2108,6 +2226,11 @@
           <t>https://lume.ufrgs.br/handle/10183/94761 ; https://revistas.unisinos.br/index.php/gaea/article/download/gaea.2016.91.02/5352/40172</t>
         </is>
       </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>WILNER, E.; LEMOS, V.B.; SCOMAZZON, A.K. 2016. Associações naturais de conodontes Mesogondolella spp., Grupo Itararé, Cisuraliano da Bacia do Paraná. Gaea — Journal of Geoscience, 9(1), 30–36. DOI: 10.4013/gaea.2016.91.02 [Fonte primária]. Disponível em: https://revistas.unisinos.br/index.php/gaea/article/view/gaea.2016.91.02</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="40" customHeight="1">
       <c r="A27" s="10" t="inlineStr">
@@ -2170,6 +2293,11 @@
           <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M27" s="21" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="10" t="inlineStr">
@@ -2232,6 +2360,11 @@
           <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M28" s="21" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="40" customHeight="1">
       <c r="A29" s="10" t="inlineStr">
@@ -2294,6 +2427,11 @@
           <t>https://www.researchgate.net/publication/260136127_Esfenofitas_da_Formacao_Rio_Bonito_Permiano_Inferior_na_regiao_de_Taio_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M29" s="21" t="inlineStr">
+        <is>
+          <t>BOARDMAN, D.R.; IANNUZZI, R.; DUTRA, T.L. 2007. Esfenófitas da Formação Rio Bonito (Permiano Inferior) na região de Taió, Santa Catarina, Brasil. Revista Brasileira de Paleontologia, 10(1), 9–20. DOI: 10.4072/rbp.2007.1.02 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/260136127</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="40" customHeight="1">
       <c r="A30" s="10" t="inlineStr">
@@ -2356,6 +2494,11 @@
           <t>https://www.researchgate.net/publication/260136127_Esfenofitas_da_Formacao_Rio_Bonito_Permiano_Inferior_na_regiao_de_Taio_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M30" s="21" t="inlineStr">
+        <is>
+          <t>BOARDMAN, D.R.; IANNUZZI, R.; DUTRA, T.L. 2007. Esfenófitas da Formação Rio Bonito (Permiano Inferior) na região de Taió, Santa Catarina, Brasil. Revista Brasileira de Paleontologia, 10(1), 9–20. DOI: 10.4072/rbp.2007.1.02 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/260136127</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="40" customHeight="1">
       <c r="A31" s="10" t="inlineStr">
@@ -2418,6 +2561,11 @@
           <t>https://eventos.utfpr.edu.br/sicite/sicite2019/paper/download/4948/1255 (Taxonomia de moluscos bivalves permianos de Itaiópolis, SC)</t>
         </is>
       </c>
+      <c r="M31" s="21" t="inlineStr">
+        <is>
+          <t>AGUIAR, R. et al. 2019. Taxonomia de moluscos bivalves permianos da Formação Rio do Rasto em Itaiópolis, SC. In: Resumos, XXIV SICITE — Semana de Iniciação Científica e Tecnológica, Universidade Tecnológica Federal do Paraná (UTFPR). [Fonte primária — publicação em anais de evento acadêmico, não indexada em periódico com DOI]. Disponível em: https://eventos.utfpr.edu.br/sicite/sicite2019/paper/download/4948/1255</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="40" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
@@ -2480,6 +2628,11 @@
           <t>https://eventos.utfpr.edu.br/sicite/sicite2019/paper/download/4948/1255 (Taxonomia de moluscos bivalves permianos de Itaiópolis, SC)</t>
         </is>
       </c>
+      <c r="M32" s="21" t="inlineStr">
+        <is>
+          <t>AGUIAR, R. et al. 2019. Taxonomia de moluscos bivalves permianos da Formação Rio do Rasto em Itaiópolis, SC. In: Resumos, XXIV SICITE — Semana de Iniciação Científica e Tecnológica, Universidade Tecnológica Federal do Paraná (UTFPR). [Fonte primária — publicação em anais de evento acadêmico, não indexada em periódico com DOI]. Disponível em: https://eventos.utfpr.edu.br/sicite/sicite2019/paper/download/4948/1255</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="40" customHeight="1">
       <c r="A33" s="10" t="inlineStr">
@@ -2542,6 +2695,11 @@
           <t>https://eventos.utfpr.edu.br/sicite/sicite2019/paper/download/4948/1255 (Taxonomia de moluscos bivalves permianos de Itaiópolis, SC)</t>
         </is>
       </c>
+      <c r="M33" s="21" t="inlineStr">
+        <is>
+          <t>AGUIAR, R. et al. 2019. Taxonomia de moluscos bivalves permianos da Formação Rio do Rasto em Itaiópolis, SC. In: Resumos, XXIV SICITE — Semana de Iniciação Científica e Tecnológica, Universidade Tecnológica Federal do Paraná (UTFPR). [Fonte primária — publicação em anais de evento acadêmico, não indexada em periódico com DOI]. Disponível em: https://eventos.utfpr.edu.br/sicite/sicite2019/paper/download/4948/1255</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="40" customHeight="1">
       <c r="A34" s="10" t="inlineStr">
@@ -2604,6 +2762,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M34" s="21" t="inlineStr">
+        <is>
+          <t>REED, F.R.C. 1930. Fossil fauna from Permian beds in the State of Santa Catharina, Brazil. Geological Magazine, 67(793), 310–322. DOI: 10.1017/S0016756800100968 [Fonte primária]. | KEGEL, W.; COSTA, M.E. 1951. Bivalves do Grupo Passa Dois, Permiano do Paraná. Boletim DGM/DNPM, n. 143. [Fonte primária — sem DOI, publicação pré-digital]. | BEURLEN, K. 1954/1957. Estudos geológicos no sul do Brasil. Boletim SBG. [Fonte primária — sem DOI, publicação pré-digital]. | ROCHA-CAMPOS, A.C. 1964 (e séries subsequentes). Bivalves do Grupo Passa Dois. Bol. IGc-USP. [Fonte primária — publicação pré-digital, acesso via biblioteca IGc-USP]</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="40" customHeight="1">
       <c r="A35" s="10" t="inlineStr">
@@ -2666,6 +2829,11 @@
           <t>https://ndmais.com.br/meio-ambiente/fosseis-em-sc-ligam-regiao-sul-a-outros-continentes-do-mundo/</t>
         </is>
       </c>
+      <c r="M35" s="21" t="inlineStr">
+        <is>
+          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação jornalística: NDMAIS. 2025. Fósseis em SC ligam região sul a outros continentes do mundo. Disponível em: https://ndmais.com.br/meio-ambiente/fosseis-em-sc-ligam-regiao-sul-a-outros-continentes-do-mundo/ [Fonte secundária — aguarda publicação científica dos pesquisadores da UNESC]</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="40" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -2728,6 +2896,11 @@
           <t>https://revistas.usp.br/bigsc/en/article/view/45052 (Rohn &amp; Rösler 1986, Bol. IG-USP Sér. Cient.)</t>
         </is>
       </c>
+      <c r="M36" s="21" t="inlineStr">
+        <is>
+          <t>ROHN, R.; RÖSLER, O. 1986. Schizoneura gondwanensis Feistmantel da Formação Rio do Rasto (Bacia do Paraná, Permiano Superior) no Estado do Paraná e no norte do Estado de Santa Catarina, Brasil. Boletim IG-USP. Série Científica, São Paulo, 17, 27–66. DOI: 10.11606/issn.2316-8986.v17i0p27-66 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsc/en/article/view/45052</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="40" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
@@ -2790,6 +2963,11 @@
           <t>https://revistas.usp.br/bigsp/en/article/view/54704 (Rohn &amp; Rösler 1989, Bol. IG-USP Pub. Esp.)</t>
         </is>
       </c>
+      <c r="M37" s="21" t="inlineStr">
+        <is>
+          <t>ROHN, R.; RÖSLER, O. 1989. Novas ocorrências de plantas fósseis na Formação Rio do Rasto (Permiano Superior) em Santa Catarina. Boletim IG-USP. Publicação Especial, São Paulo, 7, 145–158. DOI: 10.11606/issn.2317-8078.v7i0p145-158 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsp/en/article/view/54704</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -2852,6 +3030,11 @@
           <t>https://revistas.usp.br/bigsp/en/article/view/54704 (Rohn &amp; Rösler 1989, Bol. IG-USP Pub. Esp.)</t>
         </is>
       </c>
+      <c r="M38" s="21" t="inlineStr">
+        <is>
+          <t>ROHN, R.; RÖSLER, O. 1989. Novas ocorrências de plantas fósseis na Formação Rio do Rasto (Permiano Superior) em Santa Catarina. Boletim IG-USP. Publicação Especial, São Paulo, 7, 145–158. DOI: 10.11606/issn.2317-8078.v7i0p145-158 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsp/en/article/view/54704</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
@@ -2914,6 +3097,11 @@
           <t>https://revistas.usp.br/bigsp/en/article/view/54704 (Rohn &amp; Rösler 1989, Bol. IG-USP Pub. Esp.)</t>
         </is>
       </c>
+      <c r="M39" s="21" t="inlineStr">
+        <is>
+          <t>ROHN, R.; RÖSLER, O. 1989. Novas ocorrências de plantas fósseis na Formação Rio do Rasto (Permiano Superior) em Santa Catarina. Boletim IG-USP. Publicação Especial, São Paulo, 7, 145–158. DOI: 10.11606/issn.2317-8078.v7i0p145-158 [Fonte primária]. Disponível em: https://revistas.usp.br/bigsp/en/article/view/54704</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="10" t="inlineStr">
@@ -2976,6 +3164,11 @@
           <t>https://www.researchgate.net/publication/348390467_Uma_nova_localidade_equivalente_ao_Folhelho_Lontras_Pensilvaniano-Cisuraliano_Bacia_do_Parana_Santa_Catarina_Brasil</t>
         </is>
       </c>
+      <c r="M40" s="21" t="inlineStr">
+        <is>
+          <t>WEINSCHÜTZ, L.C.; RICETTI, J.H.Z.; FERNANDES, A.C.S. et al. 2021. Uma nova localidade equivalente ao Folhelho Lontras (Pensilvaniano–Cisuraliano), Bacia do Paraná. In: JELINEK, A.R.; SOMMER, C.A. (Eds.), Contribuições à Geologia do Rio Grande do Sul e de Santa Catarina. Sociedade Brasileira de Geologia, Porto Alegre, pp. 199–221. [Fonte primária — capítulo de livro]. Disponível em: https://www.researchgate.net/publication/348390467</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="12" t="inlineStr">
@@ -3038,6 +3231,11 @@
           <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279 (More than fossils: Paleoburrows as geoheritage...) ; https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418 (Proposta de classificação das paleotocas) ; https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/</t>
         </is>
       </c>
+      <c r="M41" s="21" t="inlineStr">
+        <is>
+          <t>VALDATI, J.; BECHTEL, A.P.; GOMES, M.C.V.; DOS SANTOS, Y.R.F.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2024. More than fossils: Paleoburrows as geoheritage and paleoenvironmental archives in the Caminhos dos Cânions do Sul UNESCO Global Geopark, Southern Brazil. Journal of South American Earth Sciences, 149, 105205. DOI: 10.1016/j.jsames.2024.105205 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
@@ -3100,6 +3298,11 @@
           <t>Artigo original (Paula-Couto, 1980, Anais ABC 52(3):527-531) não localizado em acesso direto; citado em: https://www.academia.edu/15400290/Icnof%C3%B3sseis_paleotocas_e_crotovinas_atribu%C3%ADdos_a_mam%C3%ADferos_extintos_no_sudeste_e_sul_do_Brasil ; https://www.scielo.br/j/rbzool/a/3q86RZbNfRbQ7rBMCZHmSpP/?lang=pt</t>
         </is>
       </c>
+      <c r="M42" s="21" t="inlineStr">
+        <is>
+          <t>PAULA-COUTO, C. 1980. Pleistocene mammals from the state of Santa Catarina, Brazil. Anais da Academia Brasileira de Ciências, 52(3), 527–531. [Fonte primária — sem DOI, publicação pré-digital; localização no acesso via AABC]. Nota: artigo original não localizado em acesso aberto no levantamento desta base; citado em revisões subsequentes.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" s="12" t="inlineStr">
@@ -3162,6 +3365,11 @@
           <t>https://www.researchgate.net/publication/344329477_RECONSTITUICAO_PALEOAMBIENTAL_ATRAVES_DE_FITOLITOS_NO_SAMBAQUI_CASA_DE_PEDRA_SAO_FRANCISCO_DO_SUL-SC_BRASIL</t>
         </is>
       </c>
+      <c r="M43" s="21" t="inlineStr">
+        <is>
+          <t>MENEZES, J.B.; GARCIA, M.J.; SOUSA, S.H.M.; ANDRADE, P.C.; MAHIQUES, M.M. 2009. Dinoflagelados quaternários da plataforma de Itajaí, Estado de Santa Catarina. In: Resumos, XX Congresso Brasileiro de Paleontologia (PALEO 2009). Boletim Informativo da Sociedade Brasileira de Paleontologia, 63, pp. 9–10. [Fonte primária — publicação em anais de evento; não indexada em periódico com DOI]. Disponível em: https://sbpbrasil.org/?mdocs-file=489</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="12" t="inlineStr">
@@ -3224,6 +3432,11 @@
           <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf ; https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
         </is>
       </c>
+      <c r="M44" s="21" t="inlineStr">
+        <is>
+          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="40" customHeight="1">
       <c r="A45" s="12" t="inlineStr">
@@ -3286,6 +3499,11 @@
           <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf ; https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
         </is>
       </c>
+      <c r="M45" s="21" t="inlineStr">
+        <is>
+          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="40" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
@@ -3348,6 +3566,11 @@
           <t>https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf ; https://www.researchgate.net/publication/307526049_Anthracoblattina_Mendesi_Pinto_Et_Sedor_Blattodea_Phyloblattidae_The_most_completely_preserved_South_American_Palaeozoic_cockroach</t>
         </is>
       </c>
+      <c r="M46" s="21" t="inlineStr">
+        <is>
+          <t>RICETTI, J.H.Z.; SCHNEIDER, J.W.; IANNUZZI, R.; WEINSCHÜTZ, L.C. 2016. Anthracoblattina mendesi Pinto et Sedor (Blattodea, Phyloblattidae): the most completely preserved South American Palaeozoic cockroach. Revista Brasileira de Paleontologia, 19(2), 181–194. DOI: 10.4072/rbp.2016.2.02 [Fonte primária]. Disponível em: https://sbpbrasil.org/assets/uploads/files/03_Ricetti_et_al_pg181a194_web.pdf | OLIVEIRA, E.P. 1930. História e descripção da geologia do Brasil. Serv. Geol. Mineral., Rio de Janeiro, 109 p. [Fonte primária histórica — sem DOI, publicação pré-digital]</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="40" customHeight="1">
       <c r="A47" s="12" t="inlineStr">
@@ -3410,6 +3633,11 @@
           <t>https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller ; https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/</t>
         </is>
       </c>
+      <c r="M47" s="21" t="inlineStr">
+        <is>
+          <t>VALDATI, J. et al. 2025. Identificação de paleotoca em Lauro Müller, SC. Nota técnica/divulgação institucional, UDESC FAEd. [Fonte secundária — publicação científica indexada não localizada no levantamento desta base]. Disponível em: https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="40" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
@@ -3472,6 +3700,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compila Mouro et al. 2018/2020)</t>
         </is>
       </c>
+      <c r="M48" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="40" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
@@ -3534,6 +3767,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M49" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="40" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
@@ -3596,6 +3834,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M50" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="40" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
@@ -3658,6 +3901,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte ; https://carnetsgeol.net/cg/19/19/CG1919.pdf (Vinn et al. 2019)</t>
         </is>
       </c>
+      <c r="M51" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | VINN, O.; MOURO, L.D.; FERNANDES, A.C.S. 2019. Serpulid polychaetes from the Lontras Shale (Late Pennsylvanian–Early Cisuralian), Paraná Basin, Brazil. Carnets Geol., 19(19), 439–444. DOI: 10.4267/2042/70514 [Fonte primária]. Disponível em: https://carnetsgeol.net/cg/19/19/CG1919.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="40" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
@@ -3720,6 +3968,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M52" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="40" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
@@ -3782,6 +4035,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M53" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="40" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
@@ -3844,6 +4102,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M54" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="40" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
@@ -3906,6 +4169,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M55" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="40" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
@@ -3968,6 +4236,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M56" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="40" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
@@ -4030,6 +4303,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M57" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="40" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
@@ -4092,6 +4370,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte ; https://sbpbrasil.org/publications/index.php/rbp/article/view/327 (Pauliv et al. 2023)</t>
         </is>
       </c>
+      <c r="M58" s="21" t="inlineStr">
+        <is>
+          <t>PAULIV, V.E.; DIAS, E.V.; SEDOR, F.A.; WEINSCHÜTZ, L.C.; RIBEIRO, A.M. 2023. A new symmoriiform shark and other chondrichthyan teeth from the earliest Permian of southern Brazil. Revista Brasileira de Paleontologia, 26(3), 227–237. DOI: 10.4072/rbp.2023.3.07 [Fonte primária]. Disponível em: https://sbpbrasil.org/publications/index.php/rbp/article/view/327</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="40" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
@@ -4154,6 +4437,11 @@
           <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
         </is>
       </c>
+      <c r="M59" s="21" t="inlineStr">
+        <is>
+          <t>MALABARBA, M.C.S.L. 1988. Paleonisciformes da Formação Rio do Sul, Permiano da Bacia do Paraná, Brasil. Pesquisas, 21, 91–103. [Fonte primária — sem DOI, publicação pré-digital; UFRGS]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2. | BELTAN, L. 1975. La faune ichtyologique du Lias du Nord Viêtnam. Mém. MNHN sér. C, 33, 1–184. [Nota: Beltan 1975 descreve Irajapintoseidon em contexto diferente; a ocorrência de I. uruguayensis em SC está citada via Mouro et al. 2020]. | MOURO, L.D. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 [Fonte primária].</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="40" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
@@ -4216,6 +4504,11 @@
           <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
         </is>
       </c>
+      <c r="M60" s="21" t="inlineStr">
+        <is>
+          <t>MALABARBA, M.C.S.L. 1988. Paleonisciformes da Formação Rio do Sul, Permiano da Bacia do Paraná, Brasil. Pesquisas, 21, 91–103. [Fonte primária — sem DOI, publicação pré-digital; UFRGS]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2. | BELTAN, L. 1975. La faune ichtyologique du Lias du Nord Viêtnam. Mém. MNHN sér. C, 33, 1–184. [Nota: Beltan 1975 descreve Irajapintoseidon em contexto diferente; a ocorrência de I. uruguayensis em SC está citada via Mouro et al. 2020]. | MOURO, L.D. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 [Fonte primária].</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="40" customHeight="1">
       <c r="A61" s="9" t="inlineStr">
@@ -4278,6 +4571,11 @@
           <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
         </is>
       </c>
+      <c r="M61" s="21" t="inlineStr">
+        <is>
+          <t>MALABARBA, M.C.S.L. 1988. Paleonisciformes da Formação Rio do Sul, Permiano da Bacia do Paraná, Brasil. Pesquisas, 21, 91–103. [Fonte primária — sem DOI, publicação pré-digital; UFRGS]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2. | BELTAN, L. 1975. La faune ichtyologique du Lias du Nord Viêtnam. Mém. MNHN sér. C, 33, 1–184. [Nota: Beltan 1975 descreve Irajapintoseidon em contexto diferente; a ocorrência de I. uruguayensis em SC está citada via Mouro et al. 2020]. | MOURO, L.D. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 [Fonte primária].</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
@@ -4340,6 +4638,11 @@
           <t>https://www.researchgate.net/publication/290429860_Larval_cases_of_caddisfly_Insecta_Trichoptera_affinity_in_Early_Permian_marine_environments_of_Gondwana</t>
         </is>
       </c>
+      <c r="M62" s="21" t="inlineStr">
+        <is>
+          <t>MALABARBA, M.C.S.L. 1988. Paleonisciformes da Formação Rio do Sul, Permiano da Bacia do Paraná, Brasil. Pesquisas, 21, 91–103. [Fonte primária — sem DOI, publicação pré-digital; UFRGS]. | HAMEL, M.-H. 2005. A new lower actinopterygian from the Early Permian of the Paraná Basin, Brazil. Journal of Vertebrate Paleontology, 25(1), 19–26. DOI: 10.1671/0272-4634(2005)025[0019:ANLAFTE]2.0.CO;2. | BELTAN, L. 1975. La faune ichtyologique du Lias du Nord Viêtnam. Mém. MNHN sér. C, 33, 1–184. [Nota: Beltan 1975 descreve Irajapintoseidon em contexto diferente; a ocorrência de I. uruguayensis em SC está citada via Mouro et al. 2020]. | MOURO, L.D. et al. 2016. Larval cases of caddisfly (Insecta: Trichoptera) affinity in Early Permian marine environments of Gondwana. Scientific Reports, 6, 19215. DOI: 10.1038/srep19215 [Fonte primária].</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
@@ -4402,6 +4705,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M63" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
@@ -4464,6 +4772,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M64" s="21" t="inlineStr">
+        <is>
+          <t>RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2011. Ocorrência de Escolecodontes (Annelida, Labidognatha) nas Formações Mafra e Rio do Sul, Permocarbonífero da Bacia do Paraná, Brasil. Boletim Informativo da Sociedade Brasileira de Paleontologia, 64, 31–32. [Fonte primária — nota em boletim de evento, sem DOI]. Nota: também citado como base do registro em Mouro et al. 2018/2020.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
@@ -4526,6 +4839,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M65" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
@@ -4588,6 +4906,11 @@
           <t>https://carnetsgeol.net/cg/19/19/CG1919.pdf (Vinn et al. 2019); https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M66" s="21" t="inlineStr">
+        <is>
+          <t>VINN, O.; MOURO, L.D.; FERNANDES, A.C.S. 2019. Serpulid polychaetes from the Lontras Shale (Late Pennsylvanian–Early Cisuralian), Paraná Basin, Brazil. Carnets Geol., 19(19), 439–444. DOI: 10.4267/2042/70514 [Fonte primária]. Disponível em: https://carnetsgeol.net/cg/19/19/CG1919.pdf</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
@@ -4650,6 +4973,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M67" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="40" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
@@ -4712,6 +5040,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M68" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="40" customHeight="1">
       <c r="A69" s="19" t="inlineStr">
@@ -4774,6 +5107,11 @@
           <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
         </is>
       </c>
+      <c r="M69" s="21" t="inlineStr">
+        <is>
+          <t>MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A.; WEINSCHÜTZ, L.C. 2018. O Folhelho Lontras (Permiano, Bacia do Paraná) e seus fósseis: descoberta, identificação e conhecimento atual. Anuário do Instituto de Geociências – UFRJ, 41(2), 636–646. DOI: 10.11137/2018_2_636_646 [Fonte primária]. Disponível em: https://revistas.ufrj.br/index.php/aigeo | MOURO, L.D.; FERNANDES, A.C.S.; CARVALHO, M.A. et al. 2020. Lontras Shale (Paraná Basin, Brazil): Insightful analysis and commentaries on paleoenvironment and fossil preservation into a deglaciation pulse of the Late Paleozoic Ice Age. Palaeogeography, Palaeoclimatology, Palaeoecology, 555, 109850. DOI: 10.1016/j.palaeo.2020.109850 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959 | MOURO, L.D. et al. 2021. Taphonomy and paleoecology of the Lontras Shale Lagerstätte: Detailing the warming peak of a Late Paleozoic Ice Age temperate fjord. Palaeogeography, Palaeoclimatology, Palaeoecology, 111326. DOI: 10.1016/j.palaeo.2022.111326 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/365485453</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="40" customHeight="1">
       <c r="A70" s="12" t="inlineStr">
@@ -4836,6 +5174,11 @@
           <t>https://ndmais.com.br/animais/descobrindo-os-antigos-habitantes-uma-jornada-pelas-especies-de-dinossauros-de-sc/ (ND Mais, 2023)</t>
         </is>
       </c>
+      <c r="M70" s="21" t="inlineStr">
+        <is>
+          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação jornalística: NDMAIS. 2023. Descobrindo os antigos habitantes: uma jornada pelas espécies de dinossauros de SC. Disponível em: https://ndmais.com.br/animais/descobrindo-os-antigos-habitantes-uma-jornada-pelas-especies-de-dinossauros-de-sc/ [Fonte secundária — sem publicação científica primária identificada no levantamento desta base]</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="40" customHeight="1">
       <c r="A71" s="12" t="inlineStr">
@@ -4898,6 +5241,11 @@
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/ ; https://portallitoralsul.com.br/noticia/2248/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio</t>
         </is>
       </c>
+      <c r="M71" s="21" t="inlineStr">
+        <is>
+          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional/jornalística: Univali / Portal Litoral Sul (2024). Disponível em: https://portallitoralsul.com.br e https://destinoflorianopolis.com.br [Fonte secundária — sem publicação científica primária identificada]</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="40" customHeight="1">
       <c r="A72" s="12" t="inlineStr">
@@ -4960,6 +5308,11 @@
           <t>https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx</t>
         </is>
       </c>
+      <c r="M72" s="21" t="inlineStr">
+        <is>
+          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional: UNIVALI. 2022. Esqueleto de Preguiça Gigante é atração no Museu Oceanográfico. Disponível em: https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx [Fonte secundária — sem publicação científica primária identificada]</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="40" customHeight="1">
       <c r="A73" s="12" t="inlineStr">
@@ -5022,6 +5375,11 @@
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/ ; https://portallitoralsul.com.br/noticia/2248/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio</t>
         </is>
       </c>
+      <c r="M73" s="21" t="inlineStr">
+        <is>
+          <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional/jornalística: Univali / Portal Litoral Sul (2024). Disponível em: https://portallitoralsul.com.br e https://destinoflorianopolis.com.br [Fonte secundária — sem publicação científica primária identificada]</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
@@ -5084,6 +5442,11 @@
           <t>https://www.researchgate.net/publication/357414983_Review_of_Oliveirania_santa_catharinae_sic_Maury_1927_and_associated_ichnofossils_Itarare_Group_Late_Carboniferous_of_Parana_Basin_Brazil</t>
         </is>
       </c>
+      <c r="M74" s="21" t="inlineStr">
+        <is>
+          <t>SILVA, R.C.; FERNANDES, A.C.S. 2021. Reavaliação de Oliveirania santa catharinae (sic) Maury 1927 e icnofósseis associados (Grupo Itararé, Carbonífero tardio da Bacia do Paraná, Brasil). Terr@Plural, 15, e2117741. DOI: 10.5212/TerraPlural.v.15.2117741.014 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/357414983</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="40" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
@@ -5146,6 +5509,11 @@
           <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
         </is>
       </c>
+      <c r="M75" s="21" t="inlineStr">
+        <is>
+          <t>BALISTIERI, P.R.M.N.; NETTO, R.G. et al. 2015. In: Lima, Netto, Corrêa &amp; Lavina (2015) — citação inferida via ScienceDirect. Fonte primária principal para este registro: LIMA, J.H.D.; NETTO, R.G.; CORRÊA, C.G.; LAVINA, E.L.C. 2015. Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil). Journal of South American Earth Sciences, 64, 339–352. DOI: 10.1016/j.jsames.2015.09.006 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="40" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
@@ -5208,6 +5576,11 @@
           <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
         </is>
       </c>
+      <c r="M76" s="21" t="inlineStr">
+        <is>
+          <t>LIMA, J.H.D.; NETTO, R.G.; CORRÊA, C.G.; LAVINA, E.L.C. 2015. Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil). Journal of South American Earth Sciences, 64, 339–352. DOI: 10.1016/j.jsames.2015.09.006 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="40" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
@@ -5270,6 +5643,11 @@
           <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
         </is>
       </c>
+      <c r="M77" s="21" t="inlineStr">
+        <is>
+          <t>LIMA, J.H.D.; NETTO, R.G.; CORRÊA, C.G.; LAVINA, E.L.C. 2015. Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil). Journal of South American Earth Sciences, 64, 339–352. DOI: 10.1016/j.jsames.2015.09.006 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="40" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
@@ -5332,6 +5710,11 @@
           <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
         </is>
       </c>
+      <c r="M78" s="21" t="inlineStr">
+        <is>
+          <t>LIMA, J.H.D.; NETTO, R.G.; CORRÊA, C.G.; LAVINA, E.L.C. 2015. Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil). Journal of South American Earth Sciences, 64, 339–352. DOI: 10.1016/j.jsames.2015.09.006 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="40" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
@@ -5394,6 +5777,11 @@
           <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
         </is>
       </c>
+      <c r="M79" s="21" t="inlineStr">
+        <is>
+          <t>LIMA, J.H.D.; NETTO, R.G.; CORRÊA, C.G.; LAVINA, E.L.C. 2015. Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil). Journal of South American Earth Sciences, 64, 339–352. DOI: 10.1016/j.jsames.2015.09.006 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="40" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
@@ -5456,6 +5844,11 @@
           <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
         </is>
       </c>
+      <c r="M80" s="21" t="inlineStr">
+        <is>
+          <t>LIMA, J.H.D.; NETTO, R.G.; CORRÊA, C.G.; LAVINA, E.L.C. 2015. Ichnology of deglaciation deposits from the Upper Carboniferous Rio do Sul Formation (Itararé Group, Paraná Basin) at central-east Santa Catarina State (southern Brazil). Journal of South American Earth Sciences, 64, 339–352. DOI: 10.1016/j.jsames.2015.09.006 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981115300274</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="40" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
@@ -5518,6 +5911,11 @@
           <t>https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/4247/Raquel%20Elisa%20Lermen3.pdf?sequence=2&amp;isAllowed=y</t>
         </is>
       </c>
+      <c r="M81" s="21" t="inlineStr">
+        <is>
+          <t>MARQUES-TOIGO, M.; DIAS-FABRÍCIO, M.E.; GUERRA-SOMMER, M.; CAZZULO-KLEPZIG, M.; PICCOLI, A.E.M. 1989. Palynology, palaeoclimatology and palaeoecology of Itararé Subgroup in Rio do Sul, SC, South Brazil. In: Anais XI Congresso Brasileiro de Paleontologia, 1989, Curitiba, pp. 757–774. [Fonte primária — publicação em anais de congresso, sem DOI]. Revisado por: LERMEN, R.E. 2006. Assinaturas icnológicas em depósitos carboníferos de Rio do Sul, SC. Dissertação de Mestrado, UNISINOS, São Leopoldo, RS. Disponível em: https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/4247/</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="40" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
@@ -5580,6 +5978,11 @@
           <t>https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/4247/Raquel%20Elisa%20Lermen3.pdf?sequence=2&amp;isAllowed=y</t>
         </is>
       </c>
+      <c r="M82" s="21" t="inlineStr">
+        <is>
+          <t>MARQUES-TOIGO, M.; DIAS-FABRÍCIO, M.E.; GUERRA-SOMMER, M.; CAZZULO-KLEPZIG, M.; PICCOLI, A.E.M. 1989. Palynology, palaeoclimatology and palaeoecology of Itararé Subgroup in Rio do Sul, SC, South Brazil. In: Anais XI Congresso Brasileiro de Paleontologia, 1989, Curitiba, pp. 757–774. [Fonte primária — publicação em anais de congresso, sem DOI]. Revisado por: LERMEN, R.E. 2006. Assinaturas icnológicas em depósitos carboníferos de Rio do Sul, SC. Dissertação de Mestrado, UNISINOS, São Leopoldo, RS. Disponível em: https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/4247/</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="40" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
@@ -5642,6 +6045,11 @@
           <t>https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/4247/Raquel%20Elisa%20Lermen3.pdf?sequence=2&amp;isAllowed=y</t>
         </is>
       </c>
+      <c r="M83" s="21" t="inlineStr">
+        <is>
+          <t>MARQUES-TOIGO, M.; DIAS-FABRÍCIO, M.E.; GUERRA-SOMMER, M.; CAZZULO-KLEPZIG, M.; PICCOLI, A.E.M. 1989. Palynology, palaeoclimatology and palaeoecology of Itararé Subgroup in Rio do Sul, SC, South Brazil. In: Anais XI Congresso Brasileiro de Paleontologia, 1989, Curitiba, pp. 757–774. [Fonte primária — publicação em anais de congresso, sem DOI]. Revisado por: LERMEN, R.E. 2006. Assinaturas icnológicas em depósitos carboníferos de Rio do Sul, SC. Dissertação de Mestrado, UNISINOS, São Leopoldo, RS. Disponível em: https://repositorio.jesuita.org.br/bitstream/handle/UNISINOS/4247/</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="40" customHeight="1">
       <c r="A84" s="20" t="inlineStr">
@@ -5704,6 +6112,11 @@
           <t>https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/</t>
         </is>
       </c>
+      <c r="M84" s="21" t="inlineStr">
+        <is>
+          <t>VALDATI, J.; BECHTEL, A.P.; GOMES, M.C.V.; DOS SANTOS, Y.R.F.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2024. More than fossils: Paleoburrows as geoheritage and paleoenvironmental archives in the Caminhos dos Cânions do Sul UNESCO Global Geopark, Southern Brazil. Journal of South American Earth Sciences, 149, 105205. DOI: 10.1016/j.jsames.2024.105205 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="40" customHeight="1">
       <c r="A85" s="20" t="inlineStr">
@@ -5766,6 +6179,11 @@
           <t>https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/</t>
         </is>
       </c>
+      <c r="M85" s="21" t="inlineStr">
+        <is>
+          <t>VALDATI, J.; BECHTEL, A.P.; GOMES, M.C.V.; DOS SANTOS, Y.R.F.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2024. More than fossils: Paleoburrows as geoheritage and paleoenvironmental archives in the Caminhos dos Cânions do Sul UNESCO Global Geopark, Southern Brazil. Journal of South American Earth Sciences, 149, 105205. DOI: 10.1016/j.jsames.2024.105205 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="40" customHeight="1">
       <c r="A86" s="20" t="inlineStr">
@@ -5828,6 +6246,11 @@
           <t>https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/ ; https://circuitomt.com.br/cavernas-pre-historicas-de-sc-guardam-registros-de-animais-gigantes-extintos-ha-10-mil-anos/</t>
         </is>
       </c>
+      <c r="M86" s="21" t="inlineStr">
+        <is>
+          <t>VALDATI, J.; BECHTEL, A.P.; GOMES, M.C.V.; DOS SANTOS, Y.R.F.; RICETTI, J.H.Z.; WEINSCHÜTZ, L.C. 2024. More than fossils: Paleoburrows as geoheritage and paleoenvironmental archives in the Caminhos dos Cânions do Sul UNESCO Global Geopark, Southern Brazil. Journal of South American Earth Sciences, 149, 105205. DOI: 10.1016/j.jsames.2024.105205 [Fonte primária]. Disponível em: https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279 | Divulgação jornalística: NDMAIS. 2025. Cavernas em SC guardam rastros de preguiças e tatus gigantes. Disponível em: https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/ [Fonte secundária complementar]</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="40" customHeight="1">
       <c r="A87" s="4" t="inlineStr">
@@ -5890,6 +6313,11 @@
           <t>https://www.researchgate.net/publication/234111844_Depositional_age_and_provenance_of_the_Itajai_Basin_Santa_Catarina_State_Brazil_Implications_for_SW_Gondwana_correlation ; https://www.sciencedirect.com/science/article/abs/pii/S0301926810000987</t>
         </is>
       </c>
+      <c r="M87" s="21" t="inlineStr">
+        <is>
+          <t>ZUCATTI DA ROSA, A.L. 2006. Evidências de vida no Ediacarano inferior da Bacia do Itajaí, SC. Dissertação de Mestrado, Universidade do Vale do Rio dos Sinos (UNISINOS), São Leopoldo, RS, 56 p. [Fonte primária]. Disponível em: https://repositorio.jesuita.org.br/handle/UNISINOS/3142 | SANCHEZ, E.A.M. et al. 2010. Depositional age and provenance of the Itajaí Basin, Santa Catarina State, Brazil: Implications for SW Gondwana correlation. Gondwana Research, 17(1), 123–145. DOI: 10.1016/j.gr.2009.08.003 [Fonte primária]. Disponível em: https://www.researchgate.net/publication/234111844</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="40" customHeight="1">
       <c r="A88" s="10" t="inlineStr">
@@ -5952,6 +6380,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M88" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="40" customHeight="1">
       <c r="A89" s="10" t="inlineStr">
@@ -6014,6 +6447,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M89" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="40" customHeight="1">
       <c r="A90" s="10" t="inlineStr">
@@ -6076,6 +6514,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M90" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="40" customHeight="1">
       <c r="A91" s="10" t="inlineStr">
@@ -6138,6 +6581,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M91" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="40" customHeight="1">
       <c r="A92" s="10" t="inlineStr">
@@ -6200,6 +6648,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M92" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="40" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
@@ -6262,6 +6715,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M93" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="40" customHeight="1">
       <c r="A94" s="10" t="inlineStr">
@@ -6324,6 +6782,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M94" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="40" customHeight="1">
       <c r="A95" s="10" t="inlineStr">
@@ -6386,6 +6849,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M95" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="40" customHeight="1">
       <c r="A96" s="10" t="inlineStr">
@@ -6448,6 +6916,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M96" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="40" customHeight="1">
       <c r="A97" s="10" t="inlineStr">
@@ -6510,6 +6983,11 @@
           <t>https://www.academia.edu/1074810/BIVALVES_F%C3%93SSEIS_COMO_INDICADORES_DA_DIN%C3%82MICA_SEDIMENTAR_UM_ESTUDO_DE_CASOS_DO_PALEOZ%C3%93ICO_SUPERIOR_DA_BACIA_DO_PARAN%C3%81_BRASIL (Ghilardi et al. — taphonomia da Fm. Rio Bonito, Taió, SC)</t>
         </is>
       </c>
+      <c r="M97" s="21" t="inlineStr">
+        <is>
+          <t>ROCHA-CAMPOS, A.C.; SIMÕES, M.G. 1993. Australomya sinuosa n. sp. (Bivalvia, Myalinidae), a new Permian bivalve from the Rio Bonito Formation, Paraná Basin, Brazil. Boletim IGc-USP. Série Científica, 24, 1–11. [Fonte primária — sem DOI, publicação pré-digital; localização via IGc-USP]. Síntese tafonômica de referência: SIMÕES, M.G.; KOWALEWSKI, M.; MELLO, L.H.C.; RODLAND, D.L.; CARLO, M. 2000. Bivalves fósseis como indicadores da dinâmica sedimentar: um estudo de casos do Paleozóico sul-brasileiro. [Capítulo em livro / Academia.edu]. Disponível em: https://www.academia.edu/1074810</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="40" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
@@ -6572,6 +7050,11 @@
           <t>https://lume.ufrgs.br/handle/10183/94761 ; https://revistas.unisinos.br/index.php/gaea/article/download/gaea.2016.91.02/5352/40172</t>
         </is>
       </c>
+      <c r="M98" s="21" t="inlineStr">
+        <is>
+          <t>WILNER, E. 2014. Conodontes do Folhelho Lontras (Grupo Itararé, Cisuraliano), Bacia do Paraná: taxonomia, bioestratigrafia e paleoecologia. Dissertação de Mestrado, Instituto de Geociências, UFRGS, Porto Alegre, RS. Disponível em: https://lume.ufrgs.br/handle/10183/94761 [Fonte primária]. | WILNER, E.; LEMOS, V.B.; SCOMAZZON, A.K. 2016. Associações naturais de conodontes Mesogondolella spp., Grupo Itararé, Cisuraliano da Bacia do Paraná. Gaea, 9(1), 30–36. DOI: 10.4013/gaea.2016.91.02 [Fonte primária].</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="40" customHeight="1">
       <c r="A99" s="19" t="inlineStr">
@@ -6634,6 +7117,11 @@
           <t>https://www.researchgate.net/publication/367511513_AS_MAIORES_PEGADAS_ATRIBUIDAS_A_MAMMALIAFORMES_DA_FORMACAO_BOTUCATU_CRETACEO_INFERIOR_ESTADO_DE_SANTA_CATARINA_BRASIL ; https://www.researchgate.net/publication/317731251_A_new_ichnotaxon_classification_of_large_mammaliform_trackways_from_the_Lower_Cretaceous_Botucatu_Formation_Parana_Basin_Brazil</t>
         </is>
       </c>
+      <c r="M99" s="21" t="inlineStr">
+        <is>
+          <t>BUCK, P.V. et al. 2022. As maiores pegadas atribuídas a Mammaliaformes da Formação Botucatu (Cretáceo Inferior), estados de Santa Catarina e São Paulo, Brasil. In: Resumos, XXVIII Congresso Brasileiro de Paleontologia. Boletim de Resumos. [Fonte primária — publicação em anais de evento; não indexada em periódico com DOI no levantamento]. Disponível em: https://www.researchgate.net/publication/367511513</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="40" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
@@ -6694,6 +7182,11 @@
       <c r="L100" s="6" t="inlineStr">
         <is>
           <t>https://scielo.br/scielo.php?pid=S1516-89132001000500010&amp;script=sci_arttext (tradução de Beurlen 1957, citando Reed)</t>
+        </is>
+      </c>
+      <c r="M100" s="21" t="inlineStr">
+        <is>
+          <t>REED, F.R.C. 1930. Fossil fauna from Permian beds in the State of Santa Catharina, Brazil. Geological Magazine, 67(793), 310–322. DOI: 10.1017/S0016756800100968 [Fonte primária]. Citado via: BEURLEN, K. 1957. Breves notícias sobre a geologia dos estados do Paraná e Santa Catarina. Ciência e Cultura, 9(1), 12–24. [Fonte secundária — tradução / nota geológica]</t>
         </is>
       </c>
     </row>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e Fontes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S179"/>
+  <dimension ref="A1:S180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>176 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
+          <t>177 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
         </is>
       </c>
     </row>
@@ -15752,8 +15752,92 @@
       </c>
       <c r="S179" s="6" t="inlineStr"/>
     </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>Holoceno</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Depósitos costeiros holocênicos — incrustações em costões rochosos do embasamento proterozóico</t>
+        </is>
+      </c>
+      <c r="C180" s="5" t="inlineStr">
+        <is>
+          <t>Vermetidae indet. (tubos de gastrópode incrustante)</t>
+        </is>
+      </c>
+      <c r="D180" s="4" t="inlineStr">
+        <is>
+          <t>Invertebrado — gastrópode incrustante</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F180" s="5" t="inlineStr">
+        <is>
+          <t>Costões rochosos entre o Cabo de Santa Marta (Laguna) e Imbituba, SC</t>
+        </is>
+      </c>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>Não informado na fonte consultada</t>
+        </is>
+      </c>
+      <c r="H180" s="5" t="inlineStr">
+        <is>
+          <t>Angulo, R.J., Giannini, P.C.F., Suguio, K. &amp; Pessenda, L.C.R. (1999) — Marine Geology 159:323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>IGc-USP; UFPR</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>últimos ~5.500 anos AP (datação radiocarbônica)</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="inlineStr">
+        <is>
+          <t>Carapaças aragoníticas de vermetídeos fósseis — gastrópodes de hábito incrustante que vivem numa faixa estreita e previsível em relação ao nível do mar, o que os torna um dos principais INDICADORES BIOLÓGICOS DE PALEONÍVEL MARINHO usados no Brasil. A curva mais completa de variação do nível relativo do mar da Região Sul foi construída a partir da altura e da datação radiocarbônica destes espécimes, coletados entre o Cabo de Santa Marta e Imbituba. O registro só é possível neste trecho porque, ao sul do cabo, a costa passa a ser dominada por planícies largas e os costões rochosos — substrato indispensável ao vermetídeo — tornam-se muito raros. RESSALVA DE ESCOPO: o SIGEP 075 é classificado como sítio SEDIMENTOLÓGICO. Os sambaquis da mesma região, embora ricos em conchas, são depósitos ARQUEOLÓGICOS (antrópicos) e por isso não integram este catálogo paleontológico.</t>
+        </is>
+      </c>
+      <c r="L180" s="5" t="inlineStr">
+        <is>
+          <t>https://sigep.eco.br/sitio075/sitio075.pdf
+https://www.sciencedirect.com/science/article/abs/pii/S0025322798001655</t>
+        </is>
+      </c>
+      <c r="M180" s="5" t="inlineStr"/>
+      <c r="N180" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="O180" s="4" t="inlineStr">
+        <is>
+          <t>Costões Laguna–Imbituba</t>
+        </is>
+      </c>
+      <c r="P180" s="4" t="inlineStr">
+        <is>
+          <t>Planície Costeira / Complexo Lagunar Centro-Sul Catarinense</t>
+        </is>
+      </c>
+      <c r="Q180" s="4" t="n">
+        <v>-28.42</v>
+      </c>
+      <c r="R180" s="4" t="n">
+        <v>-48.74</v>
+      </c>
+      <c r="S180" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:S179"/>
+  <autoFilter ref="A3:S180"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
@@ -15768,7 +15852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16159,16 +16243,20 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="B36" s="9" t="n"/>
+    </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B37" s="9" t="inlineStr"/>
+      <c r="B37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -16180,7 +16268,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -16192,7 +16280,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -16204,7 +16292,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -16216,7 +16304,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -16228,7 +16316,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -16240,12 +16328,200 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="n"/>
+      <c r="B45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legenda e Fontes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Catálogo de Fósseis SC'!$A$3:$S$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S180"/>
+  <dimension ref="A1:S183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -530,7 +530,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>177 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
+          <t>180 registros · GERADO automaticamente a partir de js/dados.js por scripts/exportar-planilha.py — NÃO editar à mão: as alterações se perdem na próxima geração. Compilado por Brenno Alef Benk.</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020) — Anuário IGEO-UFRJ; Palaeogeogr. Palaeoclimatol. Palaeoecol.</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -4116,7 +4116,9 @@
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compila Mouro et al. 2018/2020)</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compila Mouro et al. 2018/2020)</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -4143,7 +4145,11 @@
       <c r="R43" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S43" s="6" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4183,7 +4189,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020) — Anuário IGEO-UFRJ; Palaeogeogr. Palaeoclimatol. Palaeoecol.</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
@@ -4203,7 +4209,9 @@
       </c>
       <c r="L44" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M44" s="5" t="inlineStr">
@@ -4230,7 +4238,11 @@
       <c r="R44" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S44" s="4" t="inlineStr"/>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -4270,7 +4282,7 @@
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020) — Anuário IGEO-UFRJ; Palaeogeogr. Palaeoclimatol. Palaeoecol.</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
@@ -4290,7 +4302,9 @@
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M45" s="7" t="inlineStr">
@@ -4317,7 +4331,11 @@
       <c r="R45" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S45" s="6" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4377,7 +4395,7 @@
       </c>
       <c r="L46" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte
+          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)
 https://carnetsgeol.net/cg/19/19/CG1919.pdf (Vinn et al. 2019)</t>
         </is>
       </c>
@@ -4445,7 +4463,7 @@
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020) — Anuário IGEO-UFRJ; Palaeogeogr. Palaeoclimatol. Palaeoecol.</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
@@ -4465,7 +4483,9 @@
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -4492,7 +4512,11 @@
       <c r="R47" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S47" s="6" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -4532,7 +4556,7 @@
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020) — Anuário IGEO-UFRJ; Palaeogeogr. Palaeoclimatol. Palaeoecol.</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
@@ -4552,7 +4576,9 @@
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M48" s="5" t="inlineStr">
@@ -4579,7 +4605,11 @@
       <c r="R48" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S48" s="4" t="inlineStr"/>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -4619,7 +4649,7 @@
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020) — Anuário IGEO-UFRJ; Palaeogeogr. Palaeoclimatol. Palaeoecol.</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -4639,7 +4669,9 @@
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M49" s="7" t="inlineStr">
@@ -4666,7 +4698,11 @@
       <c r="R49" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S49" s="6" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4706,7 +4742,7 @@
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020) — Anuário IGEO-UFRJ; Palaeogeogr. Palaeoclimatol. Palaeoecol.</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
@@ -4726,7 +4762,9 @@
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M50" s="5" t="inlineStr">
@@ -4753,7 +4791,11 @@
       <c r="R50" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S50" s="4" t="inlineStr"/>
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -4793,7 +4835,7 @@
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2020, 2021) — Palaeogeogr. Palaeoclimatol. Palaeoecol.; Geol. RS/SC</t>
+          <t>Mouro, L.D., Fernandes, A.C.S., Rogerio, D.W. &amp; Fonseca, V.M.M. (2014) — Journal of Paleontology 88(1)</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
@@ -4808,12 +4850,13 @@
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>Quase uma centena de espécimes completos e articulados; considerados os fósseis de poríferos mais bem preservados do Brasil</t>
+          <t>PRIMEIRA esponja articulada do Paleozoico do Brasil e primeira esponja permiana articulada descrita para o país; segunda espécie conhecida do gênero. Atribuída a Hemidiscellidae (ordem Hemidiscosa). O material veio de exemplares mais completos que os analisados por Ruedemann no início do século XX, coletados no Campáleo. Quase uma centena de espécimes completos e articulados; considerados os fósseis de poríferos mais bem preservados do Brasil</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://www.cambridge.org/core/journals/journal-of-paleontology/issue/C72F5CC47805A30566C7688AAC416D80
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária)</t>
         </is>
       </c>
       <c r="M51" s="7" t="inlineStr">
@@ -4880,7 +4923,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2020, 2021) — Palaeogeogr. Palaeoclimatol. Palaeoecol.</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
@@ -4900,7 +4943,9 @@
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
@@ -4927,7 +4972,11 @@
       <c r="R52" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S52" s="4" t="inlineStr"/>
+      <c r="S52" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -4987,7 +5036,7 @@
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte
+          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)
 https://sbpbrasil.org/publications/index.php/rbp/article/view/327 (Pauliv et al. 2023)</t>
         </is>
       </c>
@@ -5407,7 +5456,7 @@
       </c>
       <c r="H58" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020, 2021)</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -5427,7 +5476,9 @@
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M58" s="5" t="inlineStr">
@@ -5454,7 +5505,11 @@
       <c r="R58" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S58" s="4" t="inlineStr"/>
+      <c r="S58" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -5494,7 +5549,7 @@
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>Ricetti, J.H.Z. &amp; Weinschütz, L.C. (2011) — Bol. Inf. SBP nº 64:31-32; Mouro et al. (2018, 2020)</t>
+          <t>Ricetti, J.H.Z. &amp; Weinschütz, L.C. (2011) — Bol. Inf. SBP nº 64:31-32; Mouro et al. (2018, 2020); Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
@@ -5514,7 +5569,9 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M59" s="7" t="inlineStr">
@@ -5541,7 +5598,11 @@
       <c r="R59" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S59" s="6" t="inlineStr"/>
+      <c r="S59" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -5581,7 +5642,7 @@
       </c>
       <c r="H60" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020)</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
@@ -5601,7 +5662,9 @@
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M60" s="5" t="inlineStr">
@@ -5628,7 +5691,11 @@
       <c r="R60" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S60" s="4" t="inlineStr"/>
+      <c r="S60" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -5689,7 +5756,7 @@
       <c r="L61" s="7" t="inlineStr">
         <is>
           <t>https://carnetsgeol.net/cg/19/19/CG1919.pdf (Vinn et al. 2019)
-https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M61" s="7" t="inlineStr">
@@ -5756,7 +5823,7 @@
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2020, 2021)</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -5776,7 +5843,9 @@
       </c>
       <c r="L62" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M62" s="5" t="inlineStr">
@@ -5803,7 +5872,11 @@
       <c r="R62" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S62" s="4" t="inlineStr"/>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -5843,7 +5916,7 @@
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2018, 2020)</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
@@ -5863,7 +5936,9 @@
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -5890,7 +5965,11 @@
       <c r="R63" s="6" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S63" s="6" t="inlineStr"/>
+      <c r="S63" s="6" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5930,7 +6009,7 @@
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>Mouro, L.D. et al. (2020, 2021)</t>
+          <t>Mouro, L.D., Pacheco, M.L.A.F., Ricetti, J.H.Z., Scomazzon, A.K., Horodyski, R.S., Fernandes, A.C.S., Carvalho, M.A., Weinschütz, L.C., Silva, M.S., Waichel, B.L. &amp; Scherer, C.M.S. (2020) — Palaeogeography, Palaeoclimatology, Palaeoecology 555:109850; Mouro, L.D., Ricetti, J.H.Z., Weinschütz, L.C. &amp; Pacheco, M.L.A.F. (2021) — "Folhelho Lontras, uma Lagerstätte do Paleozoico brasileiro", in Jelinek &amp; Sommer (eds.), Contribuições à Geologia do RS e de SC, SBG/Compasso Lugar-Cultura, p.203–221</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
@@ -5950,7 +6029,9 @@
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte</t>
+          <t>https://doi.org/10.1016/j.palaeo.2020.109850
+https://www.sciencedirect.com/science/article/abs/pii/S0031018220302959
+https://en.wikipedia.org/wiki/Lontras_Shale_Lagerst%C3%A4tte (compilação secundária — referência primária no campo Descritor)</t>
         </is>
       </c>
       <c r="M64" s="5" t="inlineStr">
@@ -5977,7 +6058,11 @@
       <c r="R64" s="4" t="n">
         <v>-49.8147</v>
       </c>
-      <c r="S64" s="4" t="inlineStr"/>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>10.1016/j.palaeo.2020.109850</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -14912,7 +14997,7 @@
       </c>
       <c r="H170" s="5" t="inlineStr">
         <is>
-          <t>Frank et al. (vários); Simão, G. (geólogo Geoparque, 2025)</t>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Frank et al. (vários); Simão, G. (geólogo Geoparque, 2025)</t>
         </is>
       </c>
       <c r="I170" s="4" t="inlineStr">
@@ -14927,12 +15012,14 @@
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>Mais de 40 estruturas identificadas; algumas interconectadas atingem até 340 m; escavadas por preguiças e tatus-gigantes extintos</t>
+          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Mais de 40 estruturas identificadas; algumas interconectadas atingem até 340 m; escavadas por preguiças e tatus-gigantes extintos</t>
         </is>
       </c>
       <c r="L170" s="5" t="inlineStr">
         <is>
-          <t>https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279 (More than fossils: Paleoburrows as geoheritage...)
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://www.sciencedirect.com/science/article/abs/pii/S0895981124004279 (More than fossils: Paleoburrows as geoheritage...)
 https://periodicos.ufpe.br/revistas/index.php/rbgfe/article/view/259418 (Proposta de classificação das paleotocas)
 https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/</t>
         </is>
@@ -14961,7 +15048,11 @@
       <c r="R170" s="4" t="n">
         <v>-49.94</v>
       </c>
-      <c r="S170" s="4" t="inlineStr"/>
+      <c r="S170" s="4" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="6" t="inlineStr">
@@ -15001,7 +15092,7 @@
       </c>
       <c r="H171" s="7" t="inlineStr">
         <is>
-          <t>Geoparque Caminhos dos Cânions do Sul (divulgação institucional); Bechtel, A.F. (doutorando em geografia, citado em reportagens, 2025/2026)</t>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Geoparque Caminhos dos Cânions do Sul (divulgação institucional); Bechtel, A.F. (doutorando em geografia, citado em reportagens, 2025/2026)</t>
         </is>
       </c>
       <c r="I171" s="6" t="inlineStr">
@@ -15016,12 +15107,14 @@
       </c>
       <c r="K171" s="7" t="inlineStr">
         <is>
-          <t>Três cavidades subterrâneas somando mais de 100 m de extensão; marcas de garras nas paredes; atribuída a tatus-gigantes (Glyptodon/Pampatherium) e/ou preguiças-gigantes</t>
+          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Três cavidades subterrâneas somando mais de 100 m de extensão; marcas de garras nas paredes; atribuída a tatus-gigantes (Glyptodon/Pampatherium) e/ou preguiças-gigantes</t>
         </is>
       </c>
       <c r="L171" s="7" t="inlineStr">
         <is>
-          <t>https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/</t>
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/</t>
         </is>
       </c>
       <c r="M171" s="7" t="inlineStr">
@@ -15048,7 +15141,11 @@
       <c r="R171" s="6" t="n">
         <v>-49.5444</v>
       </c>
-      <c r="S171" s="6" t="inlineStr"/>
+      <c r="S171" s="6" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -15088,7 +15185,7 @@
       </c>
       <c r="H172" s="5" t="inlineStr">
         <is>
-          <t>Geoparque Caminhos dos Cânions do Sul (divulgação institucional)</t>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: Geoparque Caminhos dos Cânions do Sul (divulgação institucional)</t>
         </is>
       </c>
       <c r="I172" s="4" t="inlineStr">
@@ -15103,12 +15200,14 @@
       </c>
       <c r="K172" s="5" t="inlineStr">
         <is>
-          <t>Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos)</t>
+          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Paleotoca de aproximadamente 48,5 m, escavada em arenitos da Fm. Botucatu; dois túneis convergindo numa câmara maior, com marcas de garras nas paredes; reocupada posteriormente por povos pré-colombianos (grafismos rupestres e baixos-relevos)</t>
         </is>
       </c>
       <c r="L172" s="5" t="inlineStr">
         <is>
-          <t>https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/</t>
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://recantodoscanyons.com.br/o-que-fazer-em-praia-grande-sc/parques/geoparque-caminho-dos-canyons-do-sul/</t>
         </is>
       </c>
       <c r="M172" s="5" t="inlineStr">
@@ -15135,7 +15234,11 @@
       <c r="R172" s="4" t="n">
         <v>-49.9183</v>
       </c>
-      <c r="S172" s="4" t="inlineStr"/>
+      <c r="S172" s="4" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="6" t="inlineStr">
@@ -15175,7 +15278,7 @@
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
-          <t>ND Mais (2025); CircuitoMT (2025), citando especialistas do Geoparque</t>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.) — ocorrência divulgada por: ND Mais (2025); CircuitoMT (2025), citando especialistas do Geoparque</t>
         </is>
       </c>
       <c r="I173" s="6" t="inlineStr">
@@ -15190,12 +15293,14 @@
       </c>
       <c r="K173" s="7" t="inlineStr">
         <is>
-          <t>Registros de paleotocas adicionais em cinco municípios do Geoparque (quatro em SC: Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande); mais de 40 estruturas catalogadas no total, algumas interconectadas atingindo até 340 m de extensão</t>
+          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Registros de paleotocas adicionais em cinco municípios do Geoparque (quatro em SC: Morro Grande, Timbé do Sul, Jacinto Machado e Praia Grande); mais de 40 estruturas catalogadas no total, algumas interconectadas atingindo até 340 m de extensão</t>
         </is>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
-          <t>https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://ndmais.com.br/animais/cavernas-em-sc-guardam-rastros-de-preguicas-e-tatus-gigantes/
 https://circuitomt.com.br/cavernas-pre-historicas-de-sc-guardam-registros-de-animais-gigantes-extintos-ha-10-mil-anos/</t>
         </is>
       </c>
@@ -15223,621 +15328,898 @@
       <c r="R173" s="6" t="n">
         <v>-49.8167</v>
       </c>
-      <c r="S173" s="6" t="inlineStr"/>
+      <c r="S173" s="6" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
         <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>Depósitos cenozóicos / rochas do Planalto Serrano</t>
+        </is>
+      </c>
+      <c r="C174" s="5" t="inlineStr">
+        <is>
+          <t>Megaichnus major (paleotoca URU-01-P2)</t>
+        </is>
+      </c>
+      <c r="D174" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca (Xenarthra)</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>URU-01-P2 (designação de campo)</t>
+        </is>
+      </c>
+      <c r="F174" s="5" t="inlineStr">
+        <is>
+          <t>Paleotoca de Urubici (URU-01-P2), Urubici, SC</t>
+        </is>
+      </c>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="inlineStr">
+        <is>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="inlineStr">
+        <is>
+          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Conjunto de túneis, trincheiras e dolinas a 1.036 m de altitude, com coordenada publicada (27°57′54,7″S, 49°30′33,2″O). Serviu de laboratório para experimentos de PROPAGAÇÃO SONORA dentro da estrutura: estimativas a partir do ouvido médio de Lestodon e Glossotherium robustum indicam faixa auditiva de 44 Hz a 16.490 Hz, e os testes avaliam a hipótese de comunicação acústica entre mylodontídeos fossoriais — coerente com as evidências de vida gregária em paleotocas (Buchmann et al., 2016).</t>
+        </is>
+      </c>
+      <c r="L174" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081</t>
+        </is>
+      </c>
+      <c r="M174" s="5" t="inlineStr"/>
+      <c r="N174" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="O174" s="4" t="inlineStr">
+        <is>
+          <t>Paleotoca de Urubici (URU-01-P2)</t>
+        </is>
+      </c>
+      <c r="P174" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
+        </is>
+      </c>
+      <c r="Q174" s="4" t="n">
+        <v>-27.9652</v>
+      </c>
+      <c r="R174" s="4" t="n">
+        <v>-49.5092</v>
+      </c>
+      <c r="S174" s="4" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>Escavada na Fm. Taciba (Grupo Itararé, Permiano) — estrutura cenozóica</t>
+        </is>
+      </c>
+      <c r="C175" s="7" t="inlineStr">
+        <is>
+          <t>Megaichnus major (paleotoca de Doutor Pedrinho)</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca (Xenarthra)</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>Paleotoca de Doutor Pedrinho, Doutor Pedrinho, SC</t>
+        </is>
+      </c>
+      <c r="G175" s="6" t="inlineStr">
+        <is>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
+        </is>
+      </c>
+      <c r="I175" s="6" t="inlineStr">
+        <is>
+          <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
+        </is>
+      </c>
+      <c r="J175" s="6" t="inlineStr">
+        <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="K175" s="7" t="inlineStr">
+        <is>
+          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Paleotoca escavada no ARENITO DA FORMAÇÃO TACIBA (Permiano) — caso que ilustra bem a natureza destes icnofósseis: a estrutura é do Plioceno–Pleistoceno, mas a rocha escavada é ~270 milhões de anos mais antiga. Documentada por fotogrametria, com geração de modelo tridimensional.</t>
+        </is>
+      </c>
+      <c r="L175" s="7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://www.researchgate.net/publication/365772145_Fotogrametria_de_um_icnofossil_escavado_por_preguicas-gigantes_Megaichnus_major</t>
+        </is>
+      </c>
+      <c r="M175" s="7" t="inlineStr"/>
+      <c r="N175" s="6" t="n">
+        <v>179</v>
+      </c>
+      <c r="O175" s="6" t="inlineStr">
+        <is>
+          <t>Paleotoca de Doutor Pedrinho</t>
+        </is>
+      </c>
+      <c r="P175" s="6" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
+        </is>
+      </c>
+      <c r="Q175" s="6" t="n">
+        <v>-26.7217</v>
+      </c>
+      <c r="R175" s="6" t="n">
+        <v>-49.4794</v>
+      </c>
+      <c r="S175" s="6" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>Depósitos cenozóicos / rochas sedimentares do Planalto Norte</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>Megaichnus isp. (paleotocas de Porto União)</t>
+        </is>
+      </c>
+      <c r="D176" s="4" t="inlineStr">
+        <is>
+          <t>Icnofóssil — paleotoca (Xenarthra)</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" s="5" t="inlineStr">
+        <is>
+          <t>Paleotocas de Porto União, Porto União, SC</t>
+        </is>
+      </c>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>Estrutura in situ (icnofóssil não coletável)</t>
+        </is>
+      </c>
+      <c r="H176" s="5" t="inlineStr">
+        <is>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>UNESP-Litoral Paulista; UFRGS; UNIPAMPA</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>Plioceno–Pleistoceno</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="inlineStr">
+        <is>
+          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. Conjunto de paleotocas do Planalto Norte catarinense, analisadas em conjunto com as de União da Vitória (PR), do outro lado do rio Iguaçu. Levantadas pelo método de amostragem em bola de neve (snowball sampling), com medição de altura e largura dos túneis.</t>
+        </is>
+      </c>
+      <c r="L176" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://rsdjournal.org/rsd/article/view/19176</t>
+        </is>
+      </c>
+      <c r="M176" s="5" t="inlineStr"/>
+      <c r="N176" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="O176" s="4" t="inlineStr">
+        <is>
+          <t>Paleotocas de Porto União</t>
+        </is>
+      </c>
+      <c r="P176" s="4" t="inlineStr">
+        <is>
+          <t>Bacia do Paraná / depósitos cenozóicos sobrepostos</t>
+        </is>
+      </c>
+      <c r="Q176" s="4" t="n">
+        <v>-26.2383</v>
+      </c>
+      <c r="R176" s="4" t="n">
+        <v>-51.0772</v>
+      </c>
+      <c r="S176" s="4" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="6" t="inlineStr">
+        <is>
           <t>Pleistoceno</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="B177" s="6" t="inlineStr">
         <is>
           <t>Depósitos litorâneos / lacustres</t>
         </is>
       </c>
-      <c r="C174" s="5" t="inlineStr">
+      <c r="C177" s="7" t="inlineStr">
         <is>
           <t>Tatu-gigante (Propraopus sp. / Glyptodon sp. — osteodermos)</t>
         </is>
       </c>
-      <c r="D174" s="4" t="inlineStr">
+      <c r="D177" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — Xenarthra (Cingulata)</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
+      <c r="E177" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F174" s="5" t="inlineStr">
+      <c r="F177" s="7" t="inlineStr">
         <is>
           <t>Planície litorânea sul de SC (localidades imprecisas)</t>
         </is>
       </c>
-      <c r="G174" s="4" t="inlineStr">
+      <c r="G177" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H174" s="5" t="inlineStr">
+      <c r="H177" s="7" t="inlineStr">
         <is>
           <t>Paula-Couto, C. (1980) — Anais ABC 52(3):527-531</t>
         </is>
       </c>
-      <c r="I174" s="4" t="inlineStr">
+      <c r="I177" s="6" t="inlineStr">
         <is>
           <t>Museu Nacional / UFRJ (coleção histórica)</t>
         </is>
       </c>
-      <c r="J174" s="4" t="inlineStr">
+      <c r="J177" s="6" t="inlineStr">
         <is>
           <t>ca. 2,58 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K174" s="5" t="inlineStr">
+      <c r="K177" s="7" t="inlineStr">
         <is>
           <t>Primeiro registro de tatu-gigante para SC reportado por Paula-Couto (1980)</t>
         </is>
       </c>
-      <c r="L174" s="5" t="inlineStr">
+      <c r="L177" s="7" t="inlineStr">
         <is>
           <t>Artigo original (Paula-Couto, 1980, Anais ABC 52(3):527-531) não localizado em acesso direto
 citado em: https://www.academia.edu/15400290/Icnof%C3%B3sseis_paleotocas_e_crotovinas_atribu%C3%ADdos_a_mam%C3%ADferos_extintos_no_sudeste_e_sul_do_Brasil
 https://www.scielo.br/j/rbzool/a/3q86RZbNfRbQ7rBMCZHmSpP/?lang=pt</t>
         </is>
       </c>
-      <c r="M174" s="5" t="inlineStr">
+      <c r="M177" s="7" t="inlineStr">
         <is>
           <t>PAULA-COUTO, C. 1980. Pleistocene mammals from the state of Santa Catarina, Brazil. Anais da Academia Brasileira de Ciências, 52(3), 527–531. [Fonte primária — sem DOI, publicação pré-digital; localização no acesso via AABC]. Nota: artigo original não localizado em acesso aberto no levantamento desta base; citado em revisões subsequentes.</t>
         </is>
       </c>
-      <c r="N174" s="4" t="n">
+      <c r="N177" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="O174" s="4" t="inlineStr">
+      <c r="O177" s="6" t="inlineStr">
         <is>
           <t>Planície litorânea sul de SC</t>
         </is>
       </c>
-      <c r="P174" s="4" t="inlineStr">
+      <c r="P177" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q174" s="4" t="n">
+      <c r="Q177" s="6" t="n">
         <v>-28.95</v>
       </c>
-      <c r="R174" s="4" t="n">
+      <c r="R177" s="6" t="n">
         <v>-49.45</v>
       </c>
-      <c r="S174" s="4" t="inlineStr"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
+      <c r="S177" s="6" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B175" s="6" t="inlineStr">
+      <c r="B178" s="4" t="inlineStr">
         <is>
           <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
         </is>
       </c>
-      <c r="C175" s="7" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>Stegomastodon waringi (Holland, 1920)</t>
         </is>
       </c>
-      <c r="D175" s="6" t="inlineStr">
+      <c r="D178" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — mastodonte (Proboscidea, Gomphotheriidae)</t>
         </is>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="E178" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F175" s="7" t="inlineStr">
+      <c r="F178" s="5" t="inlineStr">
         <is>
           <t>Costa de Sombrio, SC (encontrado a ~23 m de profundidade, rede de arrasto)</t>
         </is>
       </c>
-      <c r="G175" s="6" t="inlineStr">
+      <c r="G178" s="4" t="inlineStr">
         <is>
           <t>Museu Oceanográfico Univali, Balneário Piçarras/Penha, SC</t>
         </is>
       </c>
-      <c r="H175" s="7" t="inlineStr">
+      <c r="H178" s="5" t="inlineStr">
         <is>
           <t>Soto, J. (coord. Museus Univali), divulgação Univali / imprensa regional (2024)</t>
         </is>
       </c>
-      <c r="I175" s="6" t="inlineStr">
+      <c r="I178" s="4" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J175" s="6" t="inlineStr">
+      <c r="J178" s="4" t="inlineStr">
         <is>
           <t>ca. 30.000 anos (Pleistoceno Superior)</t>
         </is>
       </c>
-      <c r="K175" s="7" t="inlineStr">
+      <c r="K178" s="5" t="inlineStr">
         <is>
           <t>Metade esquerda de mandíbula de macho adulto, achada por pescadores; espécie rara em SC, mais comum no RS; estimativa de ~5 m de comprimento e ~3,5 t</t>
         </is>
       </c>
-      <c r="L175" s="7" t="inlineStr">
+      <c r="L178" s="5" t="inlineStr">
         <is>
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/
 https://portallitoralsul.com.br/noticia/2248/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio</t>
         </is>
       </c>
-      <c r="M175" s="7" t="inlineStr">
+      <c r="M178" s="5" t="inlineStr">
         <is>
           <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional/jornalística: Univali / Portal Litoral Sul (2024). Disponível em: https://portallitoralsul.com.br e https://destinoflorianopolis.com.br [Fonte secundária — sem publicação científica primária identificada]</t>
         </is>
       </c>
-      <c r="N175" s="6" t="n">
+      <c r="N178" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="O175" s="6" t="inlineStr">
+      <c r="O178" s="4" t="inlineStr">
         <is>
           <t>Costa de Sombrio (plataforma continental)</t>
         </is>
       </c>
-      <c r="P175" s="6" t="inlineStr">
+      <c r="P178" s="4" t="inlineStr">
         <is>
           <t>Plataforma Continental — Fm. Laguna-Barreira</t>
         </is>
       </c>
-      <c r="Q175" s="6" t="n">
+      <c r="Q178" s="4" t="n">
         <v>-29.22</v>
       </c>
-      <c r="R175" s="6" t="n">
+      <c r="R178" s="4" t="n">
         <v>-49.5</v>
       </c>
-      <c r="S175" s="6" t="inlineStr"/>
-    </row>
-    <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+      <c r="S178" s="4" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B176" s="4" t="inlineStr">
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
         </is>
       </c>
-      <c r="C176" s="5" t="inlineStr">
+      <c r="C179" s="7" t="inlineStr">
         <is>
           <t>Lestodon armatus Gervais, 1855</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="D179" s="6" t="inlineStr">
         <is>
           <t>Vertebrado — preguiça-gigante (Xenarthra, Mylodontidae)</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="E179" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F176" s="5" t="inlineStr">
+      <c r="F179" s="7" t="inlineStr">
         <is>
           <t>Plataforma continental entre Passo de Torres e Araranguá, SC (rede de arrasto de camarão)</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
+      <c r="G179" s="6" t="inlineStr">
         <is>
           <t>Museu Oceanográfico Univali, Balneário Piçarras, SC</t>
         </is>
       </c>
-      <c r="H176" s="5" t="inlineStr">
+      <c r="H179" s="7" t="inlineStr">
         <is>
           <t>Divulgação Museu Oceanográfico Univali (2022)</t>
         </is>
       </c>
-      <c r="I176" s="4" t="inlineStr">
+      <c r="I179" s="6" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J176" s="4" t="inlineStr">
+      <c r="J179" s="6" t="inlineStr">
         <is>
           <t>ca. 30.000 anos (Pleistoceno Superior)</t>
         </is>
       </c>
-      <c r="K176" s="5" t="inlineStr">
+      <c r="K179" s="7" t="inlineStr">
         <is>
           <t>Pelo menos dois espécimes; primeiro registro da espécie em Santa Catarina; esqueleto montado é atração do Museu Oceanográfico Univali; estimativa de ~4,5 m de altura e ~3 t</t>
         </is>
       </c>
-      <c r="L176" s="5" t="inlineStr">
+      <c r="L179" s="7" t="inlineStr">
         <is>
           <t>https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx</t>
         </is>
       </c>
-      <c r="M176" s="5" t="inlineStr">
+      <c r="M179" s="7" t="inlineStr">
         <is>
           <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional: UNIVALI. 2022. Esqueleto de Preguiça Gigante é atração no Museu Oceanográfico. Disponível em: https://www.univali.br/noticias/Paginas/Esqueleto-de-Pregui%C3%A7a-Gigante-%C3%A9-atra%C3%A7%C3%A3o-no-Museu-Oceanogr%C3%A1fico.aspx [Fonte secundária — sem publicação científica primária identificada]</t>
         </is>
       </c>
-      <c r="N176" s="4" t="n">
+      <c r="N179" s="6" t="n">
         <v>69</v>
       </c>
-      <c r="O176" s="4" t="inlineStr">
+      <c r="O179" s="6" t="inlineStr">
         <is>
           <t>Plataforma continental Passo de Torres–Araranguá</t>
         </is>
       </c>
-      <c r="P176" s="4" t="inlineStr">
+      <c r="P179" s="6" t="inlineStr">
         <is>
           <t>Plataforma Continental — Fm. Laguna-Barreira</t>
         </is>
       </c>
-      <c r="Q176" s="4" t="n">
+      <c r="Q179" s="6" t="n">
         <v>-29.28</v>
       </c>
-      <c r="R176" s="4" t="n">
+      <c r="R179" s="6" t="n">
         <v>-49.55</v>
       </c>
-      <c r="S176" s="4" t="inlineStr"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="6" t="inlineStr">
+      <c r="S179" s="6" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
         <is>
           <t>Pleistoceno Superior</t>
         </is>
       </c>
-      <c r="B177" s="6" t="inlineStr">
+      <c r="B180" s="4" t="inlineStr">
         <is>
           <t>Fm. Laguna-Barreira (depósitos da plataforma continental)</t>
         </is>
       </c>
-      <c r="C177" s="7" t="inlineStr">
+      <c r="C180" s="5" t="inlineStr">
         <is>
           <t>Toxodon sp.</t>
         </is>
       </c>
-      <c r="D177" s="6" t="inlineStr">
+      <c r="D180" s="4" t="inlineStr">
         <is>
           <t>Vertebrado — toxodonte (Notoungulata, Toxodontidae)</t>
         </is>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E180" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr">
+      <c r="F180" s="5" t="inlineStr">
         <is>
           <t>Costa de Sombrio, SC (vértebra torácica, rede de arrasto)</t>
         </is>
       </c>
-      <c r="G177" s="6" t="inlineStr">
+      <c r="G180" s="4" t="inlineStr">
         <is>
           <t>Museu Oceanográfico Univali, Balneário Piçarras/Penha, SC</t>
         </is>
       </c>
-      <c r="H177" s="7" t="inlineStr">
+      <c r="H180" s="5" t="inlineStr">
         <is>
           <t>Soto, J. (coord. Museus Univali), divulgação Univali / imprensa regional (2024)</t>
         </is>
       </c>
-      <c r="I177" s="6" t="inlineStr">
+      <c r="I180" s="4" t="inlineStr">
         <is>
           <t>Univali</t>
         </is>
       </c>
-      <c r="J177" s="6" t="inlineStr">
+      <c r="J180" s="4" t="inlineStr">
         <is>
           <t>ca. 30.000 anos (Pleistoceno Superior)</t>
         </is>
       </c>
-      <c r="K177" s="7" t="inlineStr">
+      <c r="K180" s="5" t="inlineStr">
         <is>
           <t>Vértebra torácica recuperada junto à mandíbula de Stegomastodon waringi; toxodontes são notoungulados de grande porte, descritos como morfologicamente convergentes com hipopótamos</t>
         </is>
       </c>
-      <c r="L177" s="7" t="inlineStr">
+      <c r="L180" s="5" t="inlineStr">
         <is>
           <t>https://destinoflorianopolis.com.br/fossil-de-elefante-pre-historico-e-encontrado-em-santa-catarina/
 https://portallitoralsul.com.br/noticia/2248/fossil-de-elefante-pre-historico-e-encontrado-em-sombrio</t>
         </is>
       </c>
-      <c r="M177" s="7" t="inlineStr">
+      <c r="M180" s="5" t="inlineStr">
         <is>
           <t>Fonte primária científica indexada não localizada no levantamento desta base. Citação baseada em divulgação institucional/jornalística: Univali / Portal Litoral Sul (2024). Disponível em: https://portallitoralsul.com.br e https://destinoflorianopolis.com.br [Fonte secundária — sem publicação científica primária identificada]</t>
         </is>
       </c>
-      <c r="N177" s="6" t="n">
+      <c r="N180" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="O177" s="6" t="inlineStr">
+      <c r="O180" s="4" t="inlineStr">
         <is>
           <t>Costa de Sombrio (plataforma continental)</t>
         </is>
       </c>
-      <c r="P177" s="6" t="inlineStr">
+      <c r="P180" s="4" t="inlineStr">
         <is>
           <t>Plataforma Continental — Fm. Laguna-Barreira</t>
         </is>
       </c>
-      <c r="Q177" s="6" t="n">
+      <c r="Q180" s="4" t="n">
         <v>-29.22</v>
       </c>
-      <c r="R177" s="6" t="n">
+      <c r="R180" s="4" t="n">
         <v>-49.5</v>
       </c>
-      <c r="S177" s="6" t="inlineStr"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
+      <c r="S180" s="4" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>Pleistoceno–Holoceno</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>Planície costeira sul de SC (depósitos lagunares)</t>
         </is>
       </c>
-      <c r="C178" s="5" t="inlineStr">
+      <c r="C181" s="7" t="inlineStr">
         <is>
           <t>Registro paleoambiental (fitólitos, palinomorfos)</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="D181" s="6" t="inlineStr">
         <is>
           <t>Microfóssil — material bioestratifráfico</t>
         </is>
       </c>
-      <c r="E178" s="4" t="inlineStr">
+      <c r="E181" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F178" s="5" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>Lagoa do Sombrio, SC</t>
         </is>
       </c>
-      <c r="G178" s="4" t="inlineStr">
+      <c r="G181" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H178" s="5" t="inlineStr">
+      <c r="H181" s="7" t="inlineStr">
         <is>
           <t>SBP Boletim nº 63 (resumo)</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr">
+      <c r="I181" s="6" t="inlineStr">
         <is>
           <t>UFRGS / UNISINOS</t>
         </is>
       </c>
-      <c r="J178" s="4" t="inlineStr">
+      <c r="J181" s="6" t="inlineStr">
         <is>
           <t>ca. 12.000 – 3.000 a</t>
         </is>
       </c>
-      <c r="K178" s="5" t="inlineStr">
+      <c r="K181" s="7" t="inlineStr">
         <is>
           <t>Indicadores de paleoníveis marinhos holocênicos na planície costeira</t>
         </is>
       </c>
-      <c r="L178" s="5" t="inlineStr">
+      <c r="L181" s="7" t="inlineStr">
         <is>
           <t>https://www.researchgate.net/publication/344329477_RECONSTITUICAO_PALEOAMBIENTAL_ATRAVES_DE_FITOLITOS_NO_SAMBAQUI_CASA_DE_PEDRA_SAO_FRANCISCO_DO_SUL-SC_BRASIL</t>
         </is>
       </c>
-      <c r="M178" s="5" t="inlineStr">
+      <c r="M181" s="7" t="inlineStr">
         <is>
           <t>MENEZES, J.B.; GARCIA, M.J.; SOUSA, S.H.M.; ANDRADE, P.C.; MAHIQUES, M.M. 2009. Dinoflagelados quaternários da plataforma de Itajaí, Estado de Santa Catarina. In: Resumos, XX Congresso Brasileiro de Paleontologia (PALEO 2009). Boletim Informativo da Sociedade Brasileira de Paleontologia, 63, pp. 9–10. [Fonte primária — publicação em anais de evento; não indexada em periódico com DOI]. Disponível em: https://sbpbrasil.org/?mdocs-file=489</t>
         </is>
       </c>
-      <c r="N178" s="4" t="n">
+      <c r="N181" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="O178" s="4" t="inlineStr">
+      <c r="O181" s="6" t="inlineStr">
         <is>
           <t>Lagoa do Sombrio</t>
         </is>
       </c>
-      <c r="P178" s="4" t="inlineStr">
+      <c r="P181" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira — Depósitos Quaternários</t>
         </is>
       </c>
-      <c r="Q178" s="4" t="n">
+      <c r="Q181" s="6" t="n">
         <v>-29.1133</v>
       </c>
-      <c r="R178" s="4" t="n">
+      <c r="R181" s="6" t="n">
         <v>-49.6306</v>
       </c>
-      <c r="S178" s="4" t="inlineStr"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="6" t="inlineStr">
+      <c r="S181" s="6" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t>Quaternário (Pleistoceno–Holoceno)</t>
         </is>
       </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="B182" s="4" t="inlineStr">
         <is>
           <t>Depósitos superficiais sobre a Fm. Rio Bonito / Depressão da Zona Carbonífera Catarinense</t>
         </is>
       </c>
-      <c r="C179" s="7" t="inlineStr">
+      <c r="C182" s="5" t="inlineStr">
         <is>
           <t>Paleotoca (icnofóssil de escavação — Xenarthra: tatus, preguiças, tamanduás)</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D182" s="4" t="inlineStr">
         <is>
           <t>Icnofóssil — estrutura de habitação (Domichnia)</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E182" s="4" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
+      <c r="F182" s="5" t="inlineStr">
         <is>
           <t>Lauro Müller, SC</t>
         </is>
       </c>
-      <c r="G179" s="6" t="inlineStr">
+      <c r="G182" s="4" t="inlineStr">
         <is>
           <t>UDESC — Laboratório de Geografia/Geologia (FAED)</t>
         </is>
       </c>
-      <c r="H179" s="7" t="inlineStr">
-        <is>
-          <t>Valdati, J. et al. (UDESC FAEd — divulgação 2025/2026)</t>
-        </is>
-      </c>
-      <c r="I179" s="6" t="inlineStr">
+      <c r="H182" s="5" t="inlineStr">
+        <is>
+          <t>Buchmann, F.S.C., Lopes, R.P. &amp; Caron, F. (2009) — Revista Brasileira de Paleontologia 12(3):247–256; Lopes, R.P., Frank, H.T., Buchmann, F.S. &amp; Caron, F. (2017) — Ichnos 24:133–145 (erige Megaichnus igen. nov.)</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
         <is>
           <t>UDESC</t>
         </is>
       </c>
-      <c r="J179" s="6" t="inlineStr">
+      <c r="J182" s="4" t="inlineStr">
         <is>
           <t>2,58 Ma – 11.700 a</t>
         </is>
       </c>
-      <c r="K179" s="7" t="inlineStr">
-        <is>
-          <t>1º registro documentado deste tipo de icnofóssil em rochas da Fm. Rio Bonito e na Depressão da Zona Carbonífera Catarinense; estrutura de habitação distinta das paleotocas já catalogadas no Geoparque Caminhos dos Cânions do Sul</t>
-        </is>
-      </c>
-      <c r="L179" s="7" t="inlineStr">
-        <is>
-          <t>https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
+      <c r="K182" s="5" t="inlineStr">
+        <is>
+          <t>ICNOTAXONOMIA: desde Lopes et al. (2017) estas estruturas têm nome formal — o icnogênero Megaichnus, dividido em M. major (atribuído a preguiças-gigantes, Mylodontidae) e M. minor (atribuído a tatus-gigantes, Cingulata). Santa Catarina e Rio Grande do Sul concentram a maior abundância conhecida de paleotocas do mundo, com várias centenas de registros em cada estado. 1º registro documentado deste tipo de icnofóssil em rochas da Fm. Rio Bonito e na Depressão da Zona Carbonífera Catarinense; estrutura de habitação distinta das paleotocas já catalogadas no Geoparque Caminhos dos Cânions do Sul</t>
+        </is>
+      </c>
+      <c r="L182" s="5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4072/rbp.2009.3.07
+https://sbpbrasil.org/publications/index.php/rbp/article/download/428/254/9081
+https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller
 https://ndmais.com.br/turismo/tunel-misterioso-em-sc-revela-marcas-pre-historicas/</t>
         </is>
       </c>
-      <c r="M179" s="7" t="inlineStr">
+      <c r="M182" s="5" t="inlineStr">
         <is>
           <t>VALDATI, J. et al. 2025. Identificação de paleotoca em Lauro Müller, SC. Nota técnica/divulgação institucional, UDESC FAEd. [Fonte secundária — publicação científica indexada não localizada no levantamento desta base]. Disponível em: https://www.udesc.br/noticia/pesquisadores_da_udesc_faed_identificam_paleotoca_em_lauro_muller</t>
         </is>
       </c>
-      <c r="N179" s="6" t="n">
+      <c r="N182" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="O179" s="6" t="inlineStr">
+      <c r="O182" s="4" t="inlineStr">
         <is>
           <t>Lauro Müller</t>
         </is>
       </c>
-      <c r="P179" s="6" t="inlineStr">
+      <c r="P182" s="4" t="inlineStr">
         <is>
           <t>Bacia do Paraná — Fm. Rio Bonito</t>
         </is>
       </c>
-      <c r="Q179" s="6" t="n">
+      <c r="Q182" s="4" t="n">
         <v>-28.4047</v>
       </c>
-      <c r="R179" s="6" t="n">
+      <c r="R182" s="4" t="n">
         <v>-49.3811</v>
       </c>
-      <c r="S179" s="6" t="inlineStr"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="inlineStr">
+      <c r="S182" s="4" t="inlineStr">
+        <is>
+          <t>10.4072/rbp.2009.3.07</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="6" t="inlineStr">
         <is>
           <t>Holoceno</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>Depósitos costeiros holocênicos — incrustações em costões rochosos do embasamento proterozóico</t>
         </is>
       </c>
-      <c r="C180" s="5" t="inlineStr">
+      <c r="C183" s="7" t="inlineStr">
         <is>
           <t>Vermetidae indet. (tubos de gastrópode incrustante)</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="D183" s="6" t="inlineStr">
         <is>
           <t>Invertebrado — gastrópode incrustante</t>
         </is>
       </c>
-      <c r="E180" s="4" t="inlineStr">
+      <c r="E183" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F180" s="5" t="inlineStr">
+      <c r="F183" s="7" t="inlineStr">
         <is>
           <t>Costões rochosos entre o Cabo de Santa Marta (Laguna) e Imbituba, SC</t>
         </is>
       </c>
-      <c r="G180" s="4" t="inlineStr">
+      <c r="G183" s="6" t="inlineStr">
         <is>
           <t>Não informado na fonte consultada</t>
         </is>
       </c>
-      <c r="H180" s="5" t="inlineStr">
+      <c r="H183" s="7" t="inlineStr">
         <is>
           <t>Angulo, R.J., Giannini, P.C.F., Suguio, K. &amp; Pessenda, L.C.R. (1999) — Marine Geology 159:323–339; sítio descrito em Giannini, P.C.F. (2002), SIGEP 075, CPRM/DNPM v.1:213–222</t>
         </is>
       </c>
-      <c r="I180" s="4" t="inlineStr">
+      <c r="I183" s="6" t="inlineStr">
         <is>
           <t>IGc-USP; UFPR</t>
         </is>
       </c>
-      <c r="J180" s="4" t="inlineStr">
+      <c r="J183" s="6" t="inlineStr">
         <is>
           <t>últimos ~5.500 anos AP (datação radiocarbônica)</t>
         </is>
       </c>
-      <c r="K180" s="5" t="inlineStr">
+      <c r="K183" s="7" t="inlineStr">
         <is>
           <t>Carapaças aragoníticas de vermetídeos fósseis — gastrópodes de hábito incrustante que vivem numa faixa estreita e previsível em relação ao nível do mar, o que os torna um dos principais INDICADORES BIOLÓGICOS DE PALEONÍVEL MARINHO usados no Brasil. A curva mais completa de variação do nível relativo do mar da Região Sul foi construída a partir da altura e da datação radiocarbônica destes espécimes, coletados entre o Cabo de Santa Marta e Imbituba. O registro só é possível neste trecho porque, ao sul do cabo, a costa passa a ser dominada por planícies largas e os costões rochosos — substrato indispensável ao vermetídeo — tornam-se muito raros. RESSALVA DE ESCOPO: o SIGEP 075 é classificado como sítio SEDIMENTOLÓGICO. Os sambaquis da mesma região, embora ricos em conchas, são depósitos ARQUEOLÓGICOS (antrópicos) e por isso não integram este catálogo paleontológico.</t>
         </is>
       </c>
-      <c r="L180" s="5" t="inlineStr">
+      <c r="L183" s="7" t="inlineStr">
         <is>
           <t>https://sigep.eco.br/sitio075/sitio075.pdf
 https://www.sciencedirect.com/science/article/abs/pii/S0025322798001655</t>
         </is>
       </c>
-      <c r="M180" s="5" t="inlineStr"/>
-      <c r="N180" s="4" t="n">
+      <c r="M183" s="7" t="inlineStr"/>
+      <c r="N183" s="6" t="n">
         <v>177</v>
       </c>
-      <c r="O180" s="4" t="inlineStr">
+      <c r="O183" s="6" t="inlineStr">
         <is>
           <t>Costões Laguna–Imbituba</t>
         </is>
       </c>
-      <c r="P180" s="4" t="inlineStr">
+      <c r="P183" s="6" t="inlineStr">
         <is>
           <t>Planície Costeira / Complexo Lagunar Centro-Sul Catarinense</t>
         </is>
       </c>
-      <c r="Q180" s="4" t="n">
+      <c r="Q183" s="6" t="n">
         <v>-28.42</v>
       </c>
-      <c r="R180" s="4" t="n">
+      <c r="R183" s="6" t="n">
         <v>-48.74</v>
       </c>
-      <c r="S180" s="4" t="inlineStr"/>
+      <c r="S183" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:S180"/>
+  <autoFilter ref="A3:S183"/>
   <mergeCells count="2">
     <mergeCell ref="A2:S2"/>
     <mergeCell ref="A1:S1"/>
@@ -15852,7 +16234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -16435,16 +16817,20 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+    </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B55" s="9" t="inlineStr"/>
+      <c r="B55" s="9" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -16456,7 +16842,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -16468,7 +16854,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -16480,7 +16866,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -16492,7 +16878,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -16504,7 +16890,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -16516,12 +16902,488 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="A62" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="B81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B83" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B92" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B94" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -2072,7 +2072,7 @@
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>Gandini et al. (2007)</t>
+          <t>Gandini, R., Netto, R.G. &amp; Souza, P.A. (2007) — "Paleoicnologia e a palinologia dos ritmitos do Grupo Itararé na pedreira de Águas Claras (Santa Catarina, Brasil)", Gaea — Journal of Geoscience (UNISINOS) 3(1):47–59</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -16234,7 +16234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B107"/>
+  <dimension ref="A1:B125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -17297,16 +17297,20 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="9" t="n"/>
+      <c r="B99" s="9" t="n"/>
+    </row>
     <row r="100">
-      <c r="A100" s="10" t="inlineStr">
+      <c r="A100" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B100" s="9" t="inlineStr"/>
+      <c r="B100" s="9" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="inlineStr">
+      <c r="A101" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -17318,7 +17322,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="11" t="inlineStr">
+      <c r="A102" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -17330,7 +17334,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="11" t="inlineStr">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -17342,7 +17346,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="11" t="inlineStr">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -17354,7 +17358,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="11" t="inlineStr">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -17366,7 +17370,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="11" t="inlineStr">
+      <c r="A106" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -17378,12 +17382,200 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="11" t="inlineStr">
+      <c r="A107" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B113" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B115" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B118" s="9" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B120" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B122" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B123" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B124" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>

--- a/fosseis_santa_catarina_enriquecido.xlsx
+++ b/fosseis_santa_catarina_enriquecido.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Metazoário — impressão corporal</t>
+          <t>Metazoário de afinidade incerta — impressão corporal</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Metazoário — impressão corporal</t>
+          <t>Metazoário de afinidade incerta — impressão corporal</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Metazoário — impressão corporal</t>
+          <t>Metazoário de afinidade incerta — impressão corporal</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Metazoário — impressão corporal (disco basal)</t>
+          <t>Metazoário de afinidade incerta — impressão corporal (disco basal)</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Metazoário — fragmento esquelético</t>
+          <t>Metazoário de afinidade incerta — fragmento esquelético</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Invertebrado / Vertebrado — biota mista</t>
+          <t>Assembleia fóssil (biota mista) — biota mista</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -16234,7 +16234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B125"/>
+  <dimension ref="A1:B143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -17489,16 +17489,20 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="B117" s="9" t="n"/>
+    </row>
     <row r="118">
-      <c r="A118" s="10" t="inlineStr">
+      <c r="A118" s="9" t="inlineStr">
         <is>
           <t>PROCEDÊNCIA DOS DADOS</t>
         </is>
       </c>
-      <c r="B118" s="9" t="inlineStr"/>
+      <c r="B118" s="9" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="11" t="inlineStr">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>Fonte única</t>
         </is>
@@ -17510,7 +17514,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="11" t="inlineStr">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>Regenerar</t>
         </is>
@@ -17522,7 +17526,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="11" t="inlineStr">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>Validar</t>
         </is>
@@ -17534,7 +17538,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="11" t="inlineStr">
+      <c r="A122" s="9" t="inlineStr">
         <is>
           <t>gerar_dados.py</t>
         </is>
@@ -17546,7 +17550,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="11" t="inlineStr">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>Citação ABNT</t>
         </is>
@@ -17558,7 +17562,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="11" t="inlineStr">
+      <c r="A124" s="9" t="inlineStr">
         <is>
           <t>Escopo</t>
         </is>
@@ -17570,12 +17574,200 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="11" t="inlineStr">
+      <c r="A125" s="9" t="inlineStr">
         <is>
           <t>Viés amostral</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="9" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B127" s="9" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="10" t="inlineStr">
+        <is>
+          <t>PROCEDÊNCIA DOS DADOS</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>Fonte única</t>
+        </is>
+      </c>
+      <c r="B137" s="9" t="inlineStr">
+        <is>
+          <t>js/dados.js. Esta planilha e data/*.json são gerados a partir dele.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>Regenerar</t>
+        </is>
+      </c>
+      <c r="B138" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/exportar-planilha.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>Validar</t>
+        </is>
+      </c>
+      <c r="B139" s="9" t="inlineStr">
+        <is>
+          <t>python3 scripts/validar.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>gerar_dados.py</t>
+        </is>
+      </c>
+      <c r="B140" s="9" t="inlineStr">
+        <is>
+          <t>OBSOLETO. Ia da planilha para data/*.json; rodá-lo sobrescreveria o banco com dados antigos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
+          <t>Citação ABNT</t>
+        </is>
+      </c>
+      <c r="B141" s="9" t="inlineStr">
+        <is>
+          <t>Preenchida nos 97 registros originais. Os acrescentados depois ainda não têm — o campo fica vazio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>Escopo</t>
+        </is>
+      </c>
+      <c r="B142" s="9" t="inlineStr">
+        <is>
+          <t>Apenas material COLETADO em Santa Catarina. Guarda em outro estado não descaracteriza o registro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>Viés amostral</t>
+        </is>
+      </c>
+      <c r="B143" s="9" t="inlineStr">
         <is>
           <t>A densidade reflete esforço de publicação, não riqueza fossilífera.</t>
         </is>
